--- a/pfmea_audited.xlsx
+++ b/pfmea_audited.xlsx
@@ -50,7 +50,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -273,10 +273,16 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00CC0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00CC0000"/>
     </font>
   </fonts>
   <fills count="17">
@@ -683,7 +689,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -692,9 +700,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -767,7 +773,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1028,6 +1034,90 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
@@ -1036,22 +1126,10 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -1064,70 +1142,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1167,6 +1181,24 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1176,24 +1208,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1231,13 +1245,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
@@ -1268,7 +1298,21 @@
     <cellStyle name="Normal 3" xfId="5"/>
     <cellStyle name="Hyperlink 2" xfId="6"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="10"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="10"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1431,9 +1475,9 @@
     </from>
     <to>
       <col>17</col>
-      <colOff>323191</colOff>
+      <colOff>327001</colOff>
       <row>2</row>
-      <rowOff>136466</rowOff>
+      <rowOff>132656</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -1474,7 +1518,7 @@
     </from>
     <to>
       <col>12</col>
-      <colOff>973276</colOff>
+      <colOff>969466</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </to>
@@ -2210,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="16.6640625" customWidth="1" min="1" max="1"/>
@@ -2232,7 +2276,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.6" customHeight="1">
-      <c r="A1" s="94" t="inlineStr">
+      <c r="A1" s="91" t="inlineStr">
         <is>
           <t>Quality Tools</t>
         </is>
@@ -2251,13 +2295,13 @@
       <c r="K1" s="19" t="n"/>
       <c r="L1" s="19" t="n"/>
       <c r="O1" s="18" t="n"/>
-      <c r="Q1" s="19" t="n"/>
       <c r="R1" s="19" t="n"/>
-      <c r="S1" s="18" t="n"/>
+      <c r="S1" s="19" t="n"/>
       <c r="T1" s="18" t="n"/>
       <c r="U1" s="18" t="n"/>
       <c r="V1" s="18" t="n"/>
       <c r="W1" s="18" t="n"/>
+      <c r="X1" s="18" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
@@ -2275,13 +2319,13 @@
       <c r="K2" s="19" t="n"/>
       <c r="L2" s="19" t="n"/>
       <c r="O2" s="18" t="n"/>
-      <c r="Q2" s="19" t="n"/>
       <c r="R2" s="19" t="n"/>
-      <c r="S2" s="18" t="n"/>
+      <c r="S2" s="19" t="n"/>
       <c r="T2" s="18" t="n"/>
       <c r="U2" s="18" t="n"/>
       <c r="V2" s="18" t="n"/>
       <c r="W2" s="18" t="n"/>
+      <c r="X2" s="18" t="n"/>
     </row>
     <row r="3" ht="13.8" customHeight="1" thickBot="1">
       <c r="A3" s="21" t="inlineStr">
@@ -2303,53 +2347,53 @@
       <c r="K3" s="22" t="n"/>
       <c r="L3" s="22" t="n"/>
       <c r="O3" s="18" t="n"/>
-      <c r="Q3" s="19" t="n"/>
       <c r="R3" s="19" t="n"/>
-      <c r="S3" s="18" t="n"/>
+      <c r="S3" s="19" t="n"/>
       <c r="T3" s="18" t="n"/>
       <c r="U3" s="18" t="n"/>
       <c r="V3" s="18" t="n"/>
       <c r="W3" s="18" t="n"/>
+      <c r="X3" s="18" t="n"/>
     </row>
     <row r="4" ht="21" customHeight="1">
-      <c r="A4" s="101" t="inlineStr">
+      <c r="A4" s="100" t="inlineStr">
         <is>
           <t xml:space="preserve">This template is for use by Product Resources to record the Process Failure Mode and Effects Analysis (DFMEA) for medical and other devices.  FMEA is also referred to as Failure Modes, Effects, and Criticality Analysis (FMECA).  </t>
         </is>
       </c>
-      <c r="B4" s="137" t="n"/>
-      <c r="C4" s="137" t="n"/>
+      <c r="B4" s="139" t="n"/>
+      <c r="C4" s="139" t="n"/>
       <c r="D4" s="18" t="n"/>
       <c r="G4" s="23" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H4" s="95" t="inlineStr">
+      <c r="H4" s="92" t="inlineStr">
         <is>
           <t>Please see the guidance in 90-2000-7.1 regarding FMEA process before beginning an FMEA</t>
         </is>
       </c>
-      <c r="I4" s="137" t="n"/>
-      <c r="J4" s="137" t="n"/>
-      <c r="K4" s="103" t="n"/>
+      <c r="I4" s="139" t="n"/>
+      <c r="J4" s="139" t="n"/>
+      <c r="K4" s="102" t="n"/>
       <c r="L4" s="24" t="n"/>
       <c r="O4" s="18" t="n"/>
-      <c r="Q4" s="109" t="inlineStr">
+      <c r="R4" s="90" t="inlineStr">
         <is>
           <t>Parameters:</t>
         </is>
       </c>
-      <c r="R4" s="138" t="n"/>
-      <c r="S4" s="138" t="n"/>
-      <c r="T4" s="138" t="n"/>
-      <c r="U4" s="139" t="n"/>
-      <c r="V4" s="109" t="inlineStr">
+      <c r="S4" s="140" t="n"/>
+      <c r="T4" s="140" t="n"/>
+      <c r="U4" s="140" t="n"/>
+      <c r="V4" s="141" t="n"/>
+      <c r="W4" s="90" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="W4" s="139" t="n"/>
+      <c r="X4" s="141" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="19" t="n"/>
@@ -2361,27 +2405,27 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H5" s="103" t="inlineStr">
+      <c r="H5" s="102" t="inlineStr">
         <is>
           <t>Initiate action to reduce the RPN</t>
         </is>
       </c>
       <c r="I5" s="19" t="n"/>
       <c r="J5" s="19" t="n"/>
-      <c r="K5" s="103" t="n"/>
+      <c r="K5" s="102" t="n"/>
       <c r="L5" s="24" t="n"/>
       <c r="O5" s="25" t="n"/>
-      <c r="Q5" s="109" t="inlineStr">
+      <c r="R5" s="90" t="inlineStr">
         <is>
           <t>RPN triggering requiring mitigation action:</t>
         </is>
       </c>
-      <c r="R5" s="138" t="n"/>
-      <c r="S5" s="138" t="n"/>
-      <c r="T5" s="138" t="n"/>
-      <c r="U5" s="138" t="n"/>
-      <c r="V5" s="139" t="n"/>
-      <c r="W5" s="26" t="n">
+      <c r="S5" s="140" t="n"/>
+      <c r="T5" s="140" t="n"/>
+      <c r="U5" s="140" t="n"/>
+      <c r="V5" s="140" t="n"/>
+      <c r="W5" s="141" t="n"/>
+      <c r="X5" s="26" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2395,53 +2439,53 @@
           <t>●</t>
         </is>
       </c>
-      <c r="H6" s="103" t="inlineStr">
+      <c r="H6" s="102" t="inlineStr">
         <is>
           <t>Re-evaluate the RPN value after completion of the recommended actions</t>
         </is>
       </c>
       <c r="I6" s="19" t="n"/>
       <c r="J6" s="19" t="n"/>
-      <c r="K6" s="103" t="n"/>
+      <c r="K6" s="102" t="n"/>
       <c r="L6" s="24" t="n"/>
       <c r="O6" s="18" t="n"/>
-      <c r="Q6" s="109" t="inlineStr">
+      <c r="R6" s="90" t="inlineStr">
         <is>
           <t>Severity (Sev) requiring mitigation action regardless of RPN:</t>
         </is>
       </c>
-      <c r="R6" s="138" t="n"/>
-      <c r="S6" s="138" t="n"/>
-      <c r="T6" s="138" t="n"/>
-      <c r="U6" s="138" t="n"/>
-      <c r="V6" s="139" t="n"/>
-      <c r="W6" s="26" t="n">
+      <c r="S6" s="140" t="n"/>
+      <c r="T6" s="140" t="n"/>
+      <c r="U6" s="140" t="n"/>
+      <c r="V6" s="140" t="n"/>
+      <c r="W6" s="141" t="n"/>
+      <c r="X6" s="26" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="15.6" customHeight="1">
-      <c r="A7" s="108" t="inlineStr">
+      <c r="A7" s="89" t="inlineStr">
         <is>
           <t>PROCESS FAILURE MODE AND EFFECTS ANALYSIS (PFMEA)</t>
         </is>
       </c>
-      <c r="B7" s="138" t="n"/>
-      <c r="C7" s="138" t="n"/>
-      <c r="D7" s="138" t="n"/>
-      <c r="G7" s="138" t="n"/>
-      <c r="H7" s="138" t="n"/>
-      <c r="I7" s="138" t="n"/>
-      <c r="J7" s="138" t="n"/>
-      <c r="K7" s="138" t="n"/>
-      <c r="L7" s="138" t="n"/>
-      <c r="O7" s="138" t="n"/>
-      <c r="Q7" s="138" t="n"/>
-      <c r="R7" s="138" t="n"/>
-      <c r="S7" s="138" t="n"/>
-      <c r="T7" s="138" t="n"/>
-      <c r="U7" s="138" t="n"/>
-      <c r="V7" s="138" t="n"/>
-      <c r="W7" s="139" t="n"/>
+      <c r="B7" s="140" t="n"/>
+      <c r="C7" s="140" t="n"/>
+      <c r="D7" s="140" t="n"/>
+      <c r="G7" s="140" t="n"/>
+      <c r="H7" s="140" t="n"/>
+      <c r="I7" s="140" t="n"/>
+      <c r="J7" s="140" t="n"/>
+      <c r="K7" s="140" t="n"/>
+      <c r="L7" s="140" t="n"/>
+      <c r="O7" s="140" t="n"/>
+      <c r="R7" s="140" t="n"/>
+      <c r="S7" s="140" t="n"/>
+      <c r="T7" s="140" t="n"/>
+      <c r="U7" s="140" t="n"/>
+      <c r="V7" s="140" t="n"/>
+      <c r="W7" s="140" t="n"/>
+      <c r="X7" s="141" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
@@ -2449,43 +2493,43 @@
           <t>Item:</t>
         </is>
       </c>
-      <c r="B8" s="87" t="inlineStr">
+      <c r="B8" s="98" t="inlineStr">
         <is>
           <t>Wheel damper</t>
         </is>
       </c>
-      <c r="C8" s="138" t="n"/>
-      <c r="D8" s="139" t="n"/>
+      <c r="C8" s="140" t="n"/>
+      <c r="D8" s="141" t="n"/>
       <c r="G8" s="28" t="n"/>
-      <c r="H8" s="88" t="inlineStr">
+      <c r="H8" s="108" t="inlineStr">
         <is>
           <t>Responsibility:</t>
         </is>
       </c>
-      <c r="I8" s="138" t="n"/>
-      <c r="J8" s="139" t="n"/>
-      <c r="K8" s="87" t="inlineStr">
+      <c r="I8" s="140" t="n"/>
+      <c r="J8" s="141" t="n"/>
+      <c r="K8" s="98" t="inlineStr">
         <is>
           <t>Donald Trump</t>
         </is>
       </c>
-      <c r="L8" s="138" t="n"/>
-      <c r="O8" s="139" t="n"/>
-      <c r="Q8" s="28" t="n"/>
-      <c r="R8" s="27" t="inlineStr">
+      <c r="L8" s="140" t="n"/>
+      <c r="O8" s="141" t="n"/>
+      <c r="R8" s="28" t="n"/>
+      <c r="S8" s="27" t="inlineStr">
         <is>
           <t>FMEA number:</t>
         </is>
       </c>
-      <c r="S8" s="87" t="inlineStr">
+      <c r="T8" s="98" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="T8" s="138" t="n"/>
-      <c r="U8" s="138" t="n"/>
-      <c r="V8" s="138" t="n"/>
-      <c r="W8" s="139" t="n"/>
+      <c r="U8" s="140" t="n"/>
+      <c r="V8" s="140" t="n"/>
+      <c r="W8" s="140" t="n"/>
+      <c r="X8" s="141" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
@@ -2493,39 +2537,39 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B9" s="87" t="inlineStr">
+      <c r="B9" s="98" t="inlineStr">
         <is>
           <t>Drive shaft</t>
         </is>
       </c>
-      <c r="C9" s="138" t="n"/>
-      <c r="D9" s="139" t="n"/>
-      <c r="G9" s="86" t="n"/>
-      <c r="H9" s="100" t="inlineStr">
+      <c r="C9" s="140" t="n"/>
+      <c r="D9" s="141" t="n"/>
+      <c r="G9" s="107" t="n"/>
+      <c r="H9" s="99" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="I9" s="138" t="n"/>
-      <c r="J9" s="139" t="n"/>
-      <c r="K9" s="87" t="inlineStr">
+      <c r="I9" s="140" t="n"/>
+      <c r="J9" s="141" t="n"/>
+      <c r="K9" s="98" t="inlineStr">
         <is>
           <t>Selva Jeyaseelan</t>
         </is>
       </c>
-      <c r="L9" s="138" t="n"/>
-      <c r="O9" s="139" t="n"/>
-      <c r="Q9" s="28" t="n"/>
-      <c r="R9" s="27" t="inlineStr">
+      <c r="L9" s="140" t="n"/>
+      <c r="O9" s="141" t="n"/>
+      <c r="R9" s="28" t="n"/>
+      <c r="S9" s="27" t="inlineStr">
         <is>
           <t>Page :</t>
         </is>
       </c>
-      <c r="S9" s="86" t="n"/>
-      <c r="T9" s="138" t="n"/>
-      <c r="U9" s="138" t="n"/>
-      <c r="V9" s="138" t="n"/>
-      <c r="W9" s="139" t="n"/>
+      <c r="T9" s="107" t="n"/>
+      <c r="U9" s="140" t="n"/>
+      <c r="V9" s="140" t="n"/>
+      <c r="W9" s="140" t="n"/>
+      <c r="X9" s="141" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
@@ -2533,37 +2577,37 @@
           <t>Core Team:</t>
         </is>
       </c>
-      <c r="B10" s="104" t="inlineStr">
+      <c r="B10" s="103" t="inlineStr">
         <is>
           <t>Sunder Pichai, Sam Altman, Selva Jeyaseelan</t>
         </is>
       </c>
-      <c r="C10" s="138" t="n"/>
-      <c r="D10" s="138" t="n"/>
-      <c r="G10" s="138" t="n"/>
-      <c r="H10" s="138" t="n"/>
-      <c r="I10" s="138" t="n"/>
-      <c r="J10" s="138" t="n"/>
-      <c r="K10" s="138" t="n"/>
-      <c r="L10" s="138" t="n"/>
-      <c r="O10" s="139" t="n"/>
-      <c r="Q10" s="28" t="n"/>
-      <c r="R10" s="27" t="inlineStr">
+      <c r="C10" s="140" t="n"/>
+      <c r="D10" s="140" t="n"/>
+      <c r="G10" s="140" t="n"/>
+      <c r="H10" s="140" t="n"/>
+      <c r="I10" s="140" t="n"/>
+      <c r="J10" s="140" t="n"/>
+      <c r="K10" s="140" t="n"/>
+      <c r="L10" s="140" t="n"/>
+      <c r="O10" s="141" t="n"/>
+      <c r="R10" s="28" t="n"/>
+      <c r="S10" s="27" t="inlineStr">
         <is>
           <t>FMEA Date (Orig):</t>
         </is>
       </c>
-      <c r="S10" s="30" t="n">
+      <c r="T10" s="30" t="n">
         <v>46270</v>
       </c>
-      <c r="T10" s="91" t="inlineStr">
+      <c r="U10" s="109" t="inlineStr">
         <is>
           <t>Rev:</t>
         </is>
       </c>
-      <c r="U10" s="139" t="n"/>
-      <c r="V10" s="92" t="n"/>
-      <c r="W10" s="139" t="n"/>
+      <c r="V10" s="141" t="n"/>
+      <c r="W10" s="110" t="n"/>
+      <c r="X10" s="141" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="28" t="n"/>
@@ -2577,196 +2621,201 @@
       <c r="K11" s="28" t="n"/>
       <c r="L11" s="28" t="n"/>
       <c r="O11" s="31" t="n"/>
-      <c r="Q11" s="28" t="n"/>
-      <c r="R11" s="27" t="inlineStr">
+      <c r="R11" s="28" t="n"/>
+      <c r="S11" s="27" t="inlineStr">
         <is>
           <t>FMEA Date (Cur):</t>
         </is>
       </c>
-      <c r="S11" s="30" t="n">
+      <c r="T11" s="30" t="n">
         <v>46270</v>
       </c>
-      <c r="T11" s="91" t="inlineStr">
+      <c r="U11" s="109" t="inlineStr">
         <is>
           <t>Rev:</t>
         </is>
       </c>
-      <c r="U11" s="139" t="n"/>
-      <c r="V11" s="92" t="n"/>
-      <c r="W11" s="139" t="n"/>
+      <c r="V11" s="141" t="n"/>
+      <c r="W11" s="110" t="n"/>
+      <c r="X11" s="141" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="140" t="inlineStr">
+      <c r="A12" s="142" t="inlineStr">
         <is>
           <t xml:space="preserve"> Process</t>
         </is>
       </c>
-      <c r="B12" s="90" t="inlineStr">
+      <c r="B12" s="85" t="inlineStr">
         <is>
           <t>Potential Failure Mode</t>
         </is>
       </c>
-      <c r="C12" s="90" t="inlineStr">
+      <c r="C12" s="85" t="inlineStr">
         <is>
           <t>Potential Effect(s) of Failure</t>
         </is>
       </c>
-      <c r="D12" s="89" t="inlineStr">
+      <c r="D12" s="95" t="inlineStr">
         <is>
           <t>Sev</t>
         </is>
       </c>
-      <c r="E12" s="141" t="inlineStr">
+      <c r="E12" s="143" t="inlineStr">
         <is>
           <t>pred sev</t>
         </is>
       </c>
-      <c r="F12" s="141" t="inlineStr">
+      <c r="F12" s="143" t="inlineStr">
         <is>
           <t>sev reasoning</t>
         </is>
       </c>
-      <c r="G12" s="89" t="inlineStr">
+      <c r="G12" s="95" t="inlineStr">
         <is>
           <t>Cls</t>
         </is>
       </c>
-      <c r="H12" s="90" t="inlineStr">
+      <c r="H12" s="85" t="inlineStr">
         <is>
           <t>Potential Cause(s)/ Mechanism(s) of Failure</t>
         </is>
       </c>
-      <c r="I12" s="90" t="inlineStr">
+      <c r="I12" s="85" t="inlineStr">
         <is>
           <t>Current 
 Process Prevention
 Controls</t>
         </is>
       </c>
-      <c r="J12" s="89" t="inlineStr">
+      <c r="J12" s="95" t="inlineStr">
         <is>
           <t>Occ</t>
         </is>
       </c>
-      <c r="K12" s="90" t="inlineStr">
+      <c r="K12" s="85" t="inlineStr">
         <is>
           <t>Current 
 Process Detection Controls
 Controls</t>
         </is>
       </c>
-      <c r="L12" s="89" t="inlineStr">
+      <c r="L12" s="95" t="inlineStr">
         <is>
           <t>Det</t>
         </is>
       </c>
-      <c r="M12" s="141" t="inlineStr">
+      <c r="M12" s="143" t="inlineStr">
         <is>
           <t>pred det</t>
         </is>
       </c>
-      <c r="N12" s="141" t="inlineStr">
+      <c r="N12" s="143" t="inlineStr">
         <is>
           <t>det reasoning</t>
         </is>
       </c>
-      <c r="O12" s="89" t="inlineStr">
+      <c r="O12" s="95" t="inlineStr">
         <is>
           <t>RPN</t>
         </is>
       </c>
-      <c r="P12" s="141" t="inlineStr">
+      <c r="P12" s="143" t="inlineStr">
         <is>
           <t>D-P gap</t>
         </is>
       </c>
-      <c r="Q12" s="90" t="inlineStr">
+      <c r="R12" s="85" t="inlineStr">
         <is>
           <t>Recommended Action(s)</t>
         </is>
       </c>
-      <c r="R12" s="90" t="inlineStr">
+      <c r="S12" s="85" t="inlineStr">
         <is>
           <t>Responsibility and Target Completion Date</t>
         </is>
       </c>
-      <c r="S12" s="93" t="inlineStr">
+      <c r="T12" s="111" t="inlineStr">
         <is>
           <t>Action Results</t>
         </is>
       </c>
-      <c r="T12" s="138" t="n"/>
-      <c r="U12" s="138" t="n"/>
-      <c r="V12" s="138" t="n"/>
-      <c r="W12" s="139" t="n"/>
+      <c r="U12" s="140" t="n"/>
+      <c r="V12" s="140" t="n"/>
+      <c r="W12" s="140" t="n"/>
+      <c r="X12" s="141" t="n"/>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="142" t="n"/>
-      <c r="B13" s="142" t="n"/>
-      <c r="C13" s="142" t="n"/>
-      <c r="D13" s="142" t="n"/>
-      <c r="E13" s="143" t="n"/>
-      <c r="F13" s="143" t="n"/>
-      <c r="G13" s="142" t="n"/>
-      <c r="H13" s="142" t="n"/>
-      <c r="I13" s="142" t="n"/>
-      <c r="J13" s="142" t="n"/>
-      <c r="K13" s="142" t="n"/>
-      <c r="L13" s="142" t="n"/>
-      <c r="M13" s="143" t="n"/>
-      <c r="N13" s="143" t="n"/>
-      <c r="O13" s="142" t="n"/>
-      <c r="P13" s="143" t="n"/>
-      <c r="Q13" s="142" t="n"/>
-      <c r="R13" s="142" t="n"/>
-      <c r="S13" s="90" t="inlineStr">
+      <c r="A13" s="144" t="n"/>
+      <c r="B13" s="144" t="n"/>
+      <c r="C13" s="144" t="n"/>
+      <c r="D13" s="144" t="n"/>
+      <c r="E13" s="145" t="n"/>
+      <c r="F13" s="145" t="n"/>
+      <c r="G13" s="144" t="n"/>
+      <c r="H13" s="144" t="n"/>
+      <c r="I13" s="144" t="n"/>
+      <c r="J13" s="144" t="n"/>
+      <c r="K13" s="144" t="n"/>
+      <c r="L13" s="144" t="n"/>
+      <c r="M13" s="145" t="n"/>
+      <c r="N13" s="145" t="n"/>
+      <c r="O13" s="144" t="n"/>
+      <c r="P13" s="145" t="n"/>
+      <c r="R13" s="144" t="n"/>
+      <c r="S13" s="144" t="n"/>
+      <c r="T13" s="85" t="inlineStr">
         <is>
           <t>Actions Taken</t>
         </is>
       </c>
-      <c r="T13" s="89" t="inlineStr">
+      <c r="U13" s="95" t="inlineStr">
         <is>
           <t>Sev</t>
         </is>
       </c>
-      <c r="U13" s="89" t="inlineStr">
+      <c r="V13" s="95" t="inlineStr">
         <is>
           <t>Occ</t>
         </is>
       </c>
-      <c r="V13" s="89" t="inlineStr">
+      <c r="W13" s="95" t="inlineStr">
         <is>
           <t>Det</t>
         </is>
       </c>
-      <c r="W13" s="89" t="inlineStr">
+      <c r="X13" s="95" t="inlineStr">
         <is>
           <t>RPN</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="118.8" customHeight="1">
-      <c r="A14" s="85" t="n"/>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>More grease in the bearning</t>
+    <row r="14" ht="92.40000000000001" customHeight="1">
+      <c r="A14" s="146" t="inlineStr">
+        <is>
+          <t>10. Grease plastic bearning</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>No grease filled in the bearing</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
-OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+          <t>S: Portion of production run may have to be scrapped (7)
+OEM: Portion of production run may have to be scrapped (7)
+EU: Degradtion of primary function (7)</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E14" s="144" t="n">
-        <v>9</v>
-      </c>
-      <c r="F14" s="145" t="inlineStr">
-        <is>
-          <t>failure effect text keywords do not match AIAG severity definition. OEM effect does not semantically match severity 9 because it states safe operation/regulatory noncompliance with warning, which is consistent with 9; however the S effect states reworked off line and accepted, which is consistent with 6, not 5. Recommended Severity: 9</t>
+        <v>7</v>
+      </c>
+      <c r="E14" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="148" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
         </is>
       </c>
       <c r="G14" s="13" t="n"/>
@@ -2787,129 +2836,697 @@
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
+          <t>Read switch to find the level of grease in the tank (2)
+Layer Process Audit (6)</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="147" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="148" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="P14" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="14" t="n"/>
+      <c r="U14" s="14" t="n"/>
+      <c r="V14" s="14" t="n"/>
+      <c r="W14" s="14" t="n"/>
+      <c r="X14" s="2">
+        <f>IF(O14*P14*Q14&gt;0,O14*P14*Q14,K14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="79.2" customHeight="1">
+      <c r="A15" s="150" t="n"/>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Less grease in the bearing</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S: Portion of production run may have to be scrapped (5)
+OEM: Portion of production run may have to be scrapped (7)
+</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="152" t="inlineStr">
+        <is>
+          <t>'Portion of production run may have to be scrapped' maps to AIAG 7. The stated severity 5 is an under-rating.</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>Severity test: Lower severity choosen</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>Preventive maintenance
+Calibration of gage</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
           <t>First Off Approval (2)
 Layered Process Audit (6)
 Calibration report (6)</t>
         </is>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M14" s="144" t="n">
+      <c r="M15" s="151" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="145" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection does not exactly match Strongest Detection Extracted. Recommended Detection: 2</t>
-        </is>
-      </c>
-      <c r="O14" s="2">
-        <f>D14*H14*J14</f>
-        <v/>
-      </c>
-      <c r="P14" s="146" t="inlineStr">
+      <c r="N15" s="152" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (5) does not exactly match Strongest Detection Extracted (2). Recommended Detection: 2</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="P15" s="149" t="inlineStr">
         <is>
           <t>no gap</t>
         </is>
       </c>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="13" t="n"/>
-      <c r="S14" s="14" t="n"/>
-      <c r="T14" s="14" t="n"/>
-      <c r="U14" s="14" t="n"/>
-      <c r="V14" s="14" t="n"/>
-      <c r="W14" s="2">
-        <f>IF(O14*P14*Q14&gt;0,O14*P14*Q14,K14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="118.8" customHeight="1">
-      <c r="A15" s="13" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
-OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" s="144" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" s="145" t="inlineStr">
-        <is>
-          <t>failure effect text keywords do not match AIAG severity definition. Check 2 failed: the (5) effect describes rework off line and accepted, which matches Severity 6, not 5. Recommended Severity: 9</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>DFMEA PFMEA Gap analysis check</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>Detection test scenario: Multiple Controls (Stated matches Weakest)</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>"Visual check by operator (8) \n Automated laser interlock in-station (3)"</t>
-        </is>
-      </c>
-      <c r="L15" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="M15" s="144" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" s="145" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (8) does not exactly match Strongest Detection Extracted (3). Recommended Detection: 3</t>
-        </is>
-      </c>
-      <c r="O15" s="2">
-        <f>D15*H15*J15</f>
-        <v/>
-      </c>
-      <c r="P15" s="146" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="Q15" s="13" t="n"/>
       <c r="R15" s="13" t="n"/>
-      <c r="S15" s="14" t="n"/>
+      <c r="S15" s="13" t="n"/>
       <c r="T15" s="14" t="n"/>
       <c r="U15" s="14" t="n"/>
       <c r="V15" s="14" t="n"/>
-      <c r="W15" s="2">
+      <c r="W15" s="14" t="n"/>
+      <c r="X15" s="2">
         <f>IF(O15*P15*Q15&gt;0,O15*P15*Q15,K15)</f>
         <v/>
       </c>
     </row>
+    <row r="16" ht="118.8" customHeight="1">
+      <c r="A16" s="144" t="n"/>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>More grease in the bearning</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="147" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="148" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Severity Test:Defect text matches AIAG standard</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Daily maintenace check sheet
+Preventive Maintenance
+Work instruction for grease refill</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>First Off Approval (2)
+Layered Process Audit (6)
+Calibration report (6)</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="151" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="152" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (5) does not exactly match Strongest Detection Extracted (2). Recommended Detection: 2</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="P16" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="14" t="n"/>
+      <c r="U16" s="14" t="n"/>
+      <c r="V16" s="14" t="n"/>
+      <c r="W16" s="14" t="n"/>
+      <c r="X16" s="2">
+        <f>IF(O16*P16*Q16&gt;0,O16*P16*Q16,K16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="105.6" customHeight="1">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: No discernible effect (1)</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="151" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="152" t="inlineStr">
+        <is>
+          <t>"A proportion of the production run may have to be reworked off line and accepted" maps to AIAG severity 6. The stated severity 5 is an under-rating.</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>Severity test scenario: perfect match</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Severe Semantic Mismatch (Over-rating)</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>"Random visual inspection by supervisor once a shift (3)"</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="N17" s="152" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. Check 2 failed: "Random visual inspection by supervisor once a shift (3)" describes a weak random audit/visual inspection, not AIAG detection level 3. Recommended Detection: 9</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="P17" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="n"/>
+      <c r="S17" s="13" t="n"/>
+      <c r="T17" s="14" t="n"/>
+      <c r="U17" s="14" t="n"/>
+      <c r="V17" s="14" t="n"/>
+      <c r="W17" s="14" t="n"/>
+      <c r="X17" s="2">
+        <f>IF(O17*P17*Q17&gt;0,O17*P17*Q17,K17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="79.2" customHeight="1">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>EU: Apperance, fit and finish type itms do not confrm, defect noticed by most of the customrs (&gt;75%) (4)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="147" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="148" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>Severity test scenario: Spelling and typo</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Severe Semantic Mismatch (Under-rating)</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>"In-station automated vision system that locks the machine if a defect is found (8)"</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" s="151" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="152" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. The text describes in-station automated lock/stop control, which aligns to AIAG 3, not 8. Recommended Detection: 3</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="P18" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="14" t="n"/>
+      <c r="U18" s="14" t="n"/>
+      <c r="V18" s="14" t="n"/>
+      <c r="W18" s="14" t="n"/>
+      <c r="X18" s="2">
+        <f>IF(O18*P18*Q18&gt;0,O18*P18*Q18,K18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="105.6" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>S: 100% of product may have to be scrapped. Line shutdown or stop ship. (8)
+OEM: A portion of the production run may have to be scrapped. (7)</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="151" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="152" t="inlineStr">
+        <is>
+          <t>'100% of product may have to be scrapped. Line shutdown or stop ship.' maps to AIAG 8, which is higher than the stated severity 7.</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>Severity test scenario: Column Mismatch (Under-reporting)</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Heavy Typographical Errors</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>"Aoutmated varible gaging with red light buzer to notfy opreator (5)"</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="147" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="148" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R19" s="13" t="n"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="14" t="n"/>
+      <c r="U19" s="14" t="n"/>
+      <c r="V19" s="14" t="n"/>
+      <c r="W19" s="14" t="n"/>
+      <c r="X19" s="2">
+        <f>IF(O19*P19*Q19&gt;0,O19*P19*Q19,K19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Mismatch	EU: Loss of primary function (product inoperable, does not affect safe operation) (4)</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="151" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="152" t="inlineStr">
+        <is>
+          <t>'Loss of primary function' maps to AIAG 8. The stated 4 is an under-rating.</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>Severity test scenario: EU: Loss of primary function (product inoperable, does not affect safe operation) (4)</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: . Multiple Controls (Stated matches Strongest)</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>"Visual check by operator (8)  Automated laser interlock in-station (3)"</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="147" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" s="148" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="P20" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="14" t="n"/>
+      <c r="U20" s="14" t="n"/>
+      <c r="V20" s="14" t="n"/>
+      <c r="W20" s="14" t="n"/>
+      <c r="X20" s="2">
+        <f>IF(O20*P20*Q20&gt;0,O20*P20*Q20,K20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="118.8" customHeight="1">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="147" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="148" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>DFMEA PFMEA Gap analysis check</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Multiple Controls (Stated matches Weakest)</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>"Visual check by operator (8) \n Automated laser interlock in-station (3)"</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" s="151" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" s="152" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (8) does not exactly match Strongest Detection Extracted (3). Recommended Detection: 3</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="P21" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="n"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="14" t="n"/>
+      <c r="U21" s="14" t="n"/>
+      <c r="V21" s="14" t="n"/>
+      <c r="W21" s="14" t="n"/>
+      <c r="X21" s="2">
+        <f>IF(O21*P21*Q21&gt;0,O21*P21*Q21,K21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="118.8" customHeight="1">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="151" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" s="152" t="inlineStr">
+        <is>
+          <t>'Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning' maps to AIAG 9, which is the highest effect described.</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>DFMEA PFMEA Gap analysis check</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Missing Brackets / Parentheses</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>"Manual attribute go/no-go gauging in station 7"</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M22" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="148" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="P22" s="153" t="inlineStr">
+        <is>
+          <t>Gap identified. Det must be &lt;3</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="14" t="n"/>
+      <c r="U22" s="14" t="n"/>
+      <c r="V22" s="14" t="n"/>
+      <c r="W22" s="14" t="n"/>
+      <c r="X22" s="2">
+        <f>IF(O22*P22*Q22&gt;0,O22*P22*Q22,K22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="92.40000000000001" customHeight="1">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>S: Portion of production run may have to be scrapped (7)
+OEM: Portion of production run may have to be scrapped (7)
+EU: Degradtion of primary function (7)</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="147" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="148" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Severity Test:Defect text matches AIAG standard</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Number Confusions (Scores mixed with specs)</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>"Check 5 times a day using a 2 mm variable gauge (6)"`</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="147" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" s="148" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="P23" s="149" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="n"/>
+      <c r="S23" s="13" t="n"/>
+      <c r="T23" s="14" t="n"/>
+      <c r="U23" s="14" t="n"/>
+      <c r="V23" s="14" t="n"/>
+      <c r="W23" s="14" t="n"/>
+      <c r="X23" s="2">
+        <f>IF(O23*P23*Q23&gt;0,O23*P23*Q23,K23)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="R6:W6"/>
+    <mergeCell ref="A7:X7"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="S12:W12"/>
-    <mergeCell ref="Q5:V5"/>
+    <mergeCell ref="W10:X10"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="L12:L13"/>
     <mergeCell ref="N12:N13"/>
     <mergeCell ref="K9:O9"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Q6:V6"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="R4:V4"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="R12:R13"/>
-    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="U11:V11"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="I12:I13"/>
     <mergeCell ref="K12:K13"/>
@@ -2917,40 +3534,51 @@
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A7:W7"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="T9:X9"/>
+    <mergeCell ref="T12:X12"/>
     <mergeCell ref="H5:J5"/>
     <mergeCell ref="K8:O8"/>
-    <mergeCell ref="V11:W11"/>
     <mergeCell ref="H12:H13"/>
+    <mergeCell ref="R5:W5"/>
     <mergeCell ref="B10:O10"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="J12:J13"/>
     <mergeCell ref="A4:C6"/>
     <mergeCell ref="P12:P13"/>
-    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="T8:X8"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="W11:X11"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="H4:J4"/>
-    <mergeCell ref="Q12:Q13"/>
+    <mergeCell ref="U10:V10"/>
     <mergeCell ref="H9:J9"/>
+    <mergeCell ref="S12:S13"/>
     <mergeCell ref="H6:J6"/>
   </mergeCells>
-  <conditionalFormatting sqref="D14:D15 K14:K15 O14:O15 R14:R15">
+  <conditionalFormatting sqref="D14:D23 R14:R23">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K14:K23">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O14:O23">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
+      <formula>#REF!</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="D14:D15 O14:O15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D14:D23 O14:O23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Sev</formula1>
     </dataValidation>
-    <dataValidation sqref="H14:H15 P14:P15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H14:H23 P14:P23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Occur</formula1>
     </dataValidation>
-    <dataValidation sqref="J14:J15 Q14:Q15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J14:J23 Q14:Q23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Det</formula1>
     </dataValidation>
   </dataValidations>
@@ -2990,48 +3618,48 @@
       </c>
     </row>
     <row r="2" ht="39" customHeight="1" thickBot="1">
-      <c r="B2" s="147" t="inlineStr">
+      <c r="B2" s="154" t="inlineStr">
         <is>
           <t>PFMEA - Detection
 The team should agree on the criteria and ranking values. Select one way and consistently apply that scale.</t>
         </is>
       </c>
-      <c r="C2" s="148" t="n"/>
-      <c r="D2" s="148" t="n"/>
-      <c r="E2" s="148" t="n"/>
-      <c r="F2" s="148" t="n"/>
-      <c r="G2" s="148" t="n"/>
-      <c r="H2" s="149" t="n"/>
+      <c r="C2" s="155" t="n"/>
+      <c r="D2" s="155" t="n"/>
+      <c r="E2" s="155" t="n"/>
+      <c r="F2" s="155" t="n"/>
+      <c r="G2" s="155" t="n"/>
+      <c r="H2" s="156" t="n"/>
       <c r="I2" s="74" t="n"/>
     </row>
     <row r="3" ht="18.6" customHeight="1" thickBot="1">
-      <c r="B3" s="132" t="inlineStr">
+      <c r="B3" s="134" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="134" t="inlineStr">
         <is>
           <t>Modified from J1739 / AS13004</t>
         </is>
       </c>
-      <c r="D3" s="149" t="n"/>
-      <c r="E3" s="122" t="inlineStr">
+      <c r="D3" s="156" t="n"/>
+      <c r="E3" s="124" t="inlineStr">
         <is>
           <t xml:space="preserve"> Mistake-proofed</t>
         </is>
       </c>
-      <c r="F3" s="122" t="inlineStr">
+      <c r="F3" s="124" t="inlineStr">
         <is>
           <t xml:space="preserve"> Gauged</t>
         </is>
       </c>
-      <c r="G3" s="122" t="inlineStr">
+      <c r="G3" s="124" t="inlineStr">
         <is>
           <t xml:space="preserve"> Manual Inspection  </t>
         </is>
       </c>
-      <c r="H3" s="122" t="inlineStr">
+      <c r="H3" s="124" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
@@ -3039,25 +3667,25 @@
       <c r="I3" s="74" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1" thickBot="1">
-      <c r="B4" s="122" t="inlineStr">
+      <c r="B4" s="124" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="C4" s="122" t="inlineStr">
+      <c r="C4" s="124" t="inlineStr">
         <is>
           <t>Likelihood of Detection by Process Control - Category</t>
         </is>
       </c>
-      <c r="D4" s="122" t="inlineStr">
+      <c r="D4" s="124" t="inlineStr">
         <is>
           <t>Likelihood of Detection by Process Control - Criteria</t>
         </is>
       </c>
-      <c r="E4" s="150" t="n"/>
-      <c r="F4" s="150" t="n"/>
-      <c r="G4" s="150" t="n"/>
-      <c r="H4" s="150" t="n"/>
+      <c r="E4" s="157" t="n"/>
+      <c r="F4" s="157" t="n"/>
+      <c r="G4" s="157" t="n"/>
+      <c r="H4" s="157" t="n"/>
       <c r="K4" s="75" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1" thickBot="1">
@@ -3076,7 +3704,7 @@
       </c>
       <c r="E5" s="77" t="n"/>
       <c r="F5" s="78" t="n"/>
-      <c r="G5" s="151" t="inlineStr">
+      <c r="G5" s="158" t="inlineStr">
         <is>
           <t xml:space="preserve">100% Human Inspection </t>
         </is>
@@ -3099,7 +3727,7 @@
       </c>
       <c r="E6" s="80" t="n"/>
       <c r="F6" s="78" t="n"/>
-      <c r="G6" s="152" t="n"/>
+      <c r="G6" s="159" t="n"/>
       <c r="H6" s="79" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1" thickBot="1">
@@ -3118,7 +3746,7 @@
       </c>
       <c r="E7" s="80" t="n"/>
       <c r="F7" s="78" t="n"/>
-      <c r="G7" s="152" t="n"/>
+      <c r="G7" s="159" t="n"/>
       <c r="H7" s="79" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" thickBot="1">
@@ -3136,12 +3764,12 @@
         </is>
       </c>
       <c r="E8" s="80" t="n"/>
-      <c r="F8" s="151" t="inlineStr">
+      <c r="F8" s="158" t="inlineStr">
         <is>
           <t>Manual gauging is used on every part</t>
         </is>
       </c>
-      <c r="G8" s="152" t="n"/>
+      <c r="G8" s="159" t="n"/>
       <c r="H8" s="79" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" thickBot="1">
@@ -3159,8 +3787,8 @@
         </is>
       </c>
       <c r="E9" s="80" t="n"/>
-      <c r="F9" s="150" t="n"/>
-      <c r="G9" s="152" t="n"/>
+      <c r="F9" s="157" t="n"/>
+      <c r="G9" s="159" t="n"/>
       <c r="H9" s="79" t="n"/>
     </row>
     <row r="10" ht="58.5" customHeight="1" thickBot="1">
@@ -3178,12 +3806,12 @@
         </is>
       </c>
       <c r="E10" s="80" t="n"/>
-      <c r="F10" s="151" t="inlineStr">
+      <c r="F10" s="158" t="inlineStr">
         <is>
           <t>Automatic gauging or controls to detect discrepant part</t>
         </is>
       </c>
-      <c r="G10" s="150" t="n"/>
+      <c r="G10" s="157" t="n"/>
       <c r="H10" s="79" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1" thickBot="1">
@@ -3200,12 +3828,12 @@
           <t>Defect (Failure Mode) detection post-processing by automated controls that will detect discrepant part and lock part to prevent further processing.</t>
         </is>
       </c>
-      <c r="E11" s="151" t="inlineStr">
+      <c r="E11" s="158" t="inlineStr">
         <is>
           <t>Controls in place for mistake proofing the assembly</t>
         </is>
       </c>
-      <c r="F11" s="152" t="n"/>
+      <c r="F11" s="159" t="n"/>
       <c r="G11" s="81" t="n"/>
       <c r="H11" s="79" t="n"/>
     </row>
@@ -3223,8 +3851,8 @@
           <t>Defect (Failure Mode) detection in-station by automated controls that will detect discrepant part and automatically lock part in station to prevent further processing.</t>
         </is>
       </c>
-      <c r="E12" s="152" t="n"/>
-      <c r="F12" s="150" t="n"/>
+      <c r="E12" s="159" t="n"/>
+      <c r="F12" s="157" t="n"/>
       <c r="G12" s="81" t="n"/>
       <c r="H12" s="79" t="n"/>
     </row>
@@ -3242,7 +3870,7 @@
           <t>Error (Cause) detection in-station by automated controls that will detect error and prevent discrepant part from being made.</t>
         </is>
       </c>
-      <c r="E13" s="152" t="n"/>
+      <c r="E13" s="159" t="n"/>
       <c r="F13" s="78" t="n"/>
       <c r="G13" s="81" t="n"/>
       <c r="H13" s="79" t="n"/>
@@ -3261,7 +3889,7 @@
           <t>Error (Cause) prevention as a result of fixture design, machine design or part design.</t>
         </is>
       </c>
-      <c r="E14" s="150" t="n"/>
+      <c r="E14" s="157" t="n"/>
       <c r="F14" s="82" t="n"/>
       <c r="G14" s="83" t="n"/>
       <c r="H14" s="79" t="n"/>
@@ -3321,7 +3949,7 @@
     <col width="17.6640625" customWidth="1" style="39" min="7" max="7"/>
     <col width="15.6640625" customWidth="1" style="39" min="8" max="8"/>
     <col width="14.88671875" customWidth="1" style="39" min="9" max="9"/>
-    <col width="30.33203125" customWidth="1" style="125" min="10" max="10"/>
+    <col width="30.33203125" customWidth="1" style="133" min="10" max="10"/>
     <col width="3.109375" customWidth="1" style="39" min="11" max="11"/>
     <col width="8.88671875" customWidth="1" style="39" min="12" max="16384"/>
   </cols>
@@ -3335,124 +3963,124 @@
       </c>
     </row>
     <row r="2" ht="41.25" customHeight="1" thickBot="1">
-      <c r="B2" s="147" t="inlineStr">
+      <c r="B2" s="154" t="inlineStr">
         <is>
           <t>PFMEA - Occurrence
 The team should agree on the criteria and ranking values. Select one way and consistently apply that scale.</t>
         </is>
       </c>
-      <c r="C2" s="148" t="n"/>
-      <c r="D2" s="148" t="n"/>
-      <c r="E2" s="148" t="n"/>
-      <c r="F2" s="148" t="n"/>
-      <c r="G2" s="148" t="n"/>
-      <c r="H2" s="148" t="n"/>
-      <c r="I2" s="148" t="n"/>
-      <c r="J2" s="149" t="n"/>
+      <c r="C2" s="155" t="n"/>
+      <c r="D2" s="155" t="n"/>
+      <c r="E2" s="155" t="n"/>
+      <c r="F2" s="155" t="n"/>
+      <c r="G2" s="155" t="n"/>
+      <c r="H2" s="155" t="n"/>
+      <c r="I2" s="155" t="n"/>
+      <c r="J2" s="156" t="n"/>
     </row>
     <row r="3" ht="26.25" customHeight="1" thickBot="1">
-      <c r="B3" s="132" t="inlineStr">
+      <c r="B3" s="134" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="134" t="inlineStr">
         <is>
           <t>J1739</t>
         </is>
       </c>
-      <c r="D3" s="132" t="inlineStr">
+      <c r="D3" s="134" t="inlineStr">
         <is>
           <t>AS13004</t>
         </is>
       </c>
-      <c r="E3" s="148" t="n"/>
-      <c r="F3" s="148" t="n"/>
-      <c r="G3" s="149" t="n"/>
-      <c r="H3" s="132" t="inlineStr">
+      <c r="E3" s="155" t="n"/>
+      <c r="F3" s="155" t="n"/>
+      <c r="G3" s="156" t="n"/>
+      <c r="H3" s="134" t="inlineStr">
         <is>
           <t>AIAG FMEA - 4th Edition</t>
         </is>
       </c>
-      <c r="I3" s="132" t="inlineStr">
+      <c r="I3" s="134" t="inlineStr">
         <is>
           <t>J1739</t>
         </is>
       </c>
-      <c r="J3" s="122" t="inlineStr">
+      <c r="J3" s="124" t="inlineStr">
         <is>
           <t>Examples</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="122" t="inlineStr">
+      <c r="B4" s="124" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="C4" s="122" t="inlineStr">
+      <c r="C4" s="124" t="inlineStr">
         <is>
           <t>Likelihood of
 Failure</t>
         </is>
       </c>
-      <c r="D4" s="122" t="inlineStr">
+      <c r="D4" s="124" t="inlineStr">
         <is>
           <t>Low volume production</t>
         </is>
       </c>
-      <c r="E4" s="149" t="n"/>
-      <c r="F4" s="122" t="inlineStr">
+      <c r="E4" s="156" t="n"/>
+      <c r="F4" s="124" t="inlineStr">
         <is>
           <t>Process PPM</t>
         </is>
       </c>
-      <c r="G4" s="122" t="inlineStr">
+      <c r="G4" s="124" t="inlineStr">
         <is>
           <t>Time-Based Example</t>
         </is>
       </c>
-      <c r="H4" s="122" t="inlineStr">
+      <c r="H4" s="124" t="inlineStr">
         <is>
           <t>High volume production</t>
         </is>
       </c>
-      <c r="I4" s="149" t="n"/>
-      <c r="J4" s="152" t="n"/>
+      <c r="I4" s="156" t="n"/>
+      <c r="J4" s="159" t="n"/>
     </row>
     <row r="5" ht="29.4" customHeight="1" thickBot="1">
-      <c r="B5" s="150" t="n"/>
-      <c r="C5" s="150" t="n"/>
-      <c r="D5" s="122" t="inlineStr">
+      <c r="B5" s="157" t="n"/>
+      <c r="C5" s="157" t="n"/>
+      <c r="D5" s="124" t="inlineStr">
         <is>
           <t>Likelihood of Cause</t>
         </is>
       </c>
-      <c r="E5" s="122" t="inlineStr">
+      <c r="E5" s="124" t="inlineStr">
         <is>
           <t>Time-Based Example</t>
         </is>
       </c>
-      <c r="F5" s="150" t="n"/>
-      <c r="G5" s="150" t="n"/>
-      <c r="H5" s="122" t="inlineStr">
+      <c r="F5" s="157" t="n"/>
+      <c r="G5" s="157" t="n"/>
+      <c r="H5" s="124" t="inlineStr">
         <is>
           <t>Likelihood of Cause</t>
         </is>
       </c>
-      <c r="I5" s="122" t="inlineStr">
+      <c r="I5" s="124" t="inlineStr">
         <is>
           <t>Incidents per item/unit</t>
         </is>
       </c>
-      <c r="J5" s="150" t="n"/>
+      <c r="J5" s="157" t="n"/>
     </row>
     <row r="6" ht="41.25" customHeight="1" thickBot="1">
       <c r="B6" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="123" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -3462,7 +4090,7 @@
           <t>100% of production</t>
         </is>
       </c>
-      <c r="E6" s="123" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per occurrence per shift</t>
         </is>
@@ -3470,7 +4098,7 @@
       <c r="F6" s="62" t="n">
         <v>500000</v>
       </c>
-      <c r="G6" s="123" t="inlineStr">
+      <c r="G6" s="131" t="inlineStr">
         <is>
           <t>&gt; 1 per occurrence per shift</t>
         </is>
@@ -3480,7 +4108,7 @@
           <t>1 in 10</t>
         </is>
       </c>
-      <c r="I6" s="123" t="inlineStr">
+      <c r="I6" s="131" t="inlineStr">
         <is>
           <t>&gt; 100 per thousand</t>
         </is>
@@ -3491,7 +4119,7 @@
       <c r="B7" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="123" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3501,7 +4129,7 @@
           <t>50% of production</t>
         </is>
       </c>
-      <c r="E7" s="123" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per occurrence per day</t>
         </is>
@@ -3509,12 +4137,12 @@
       <c r="F7" s="62" t="n">
         <v>50000</v>
       </c>
-      <c r="G7" s="123" t="inlineStr">
+      <c r="G7" s="131" t="inlineStr">
         <is>
           <t>&gt; 1 per occurrence per day</t>
         </is>
       </c>
-      <c r="H7" s="123" t="inlineStr">
+      <c r="H7" s="131" t="inlineStr">
         <is>
           <t>1 in 20</t>
         </is>
@@ -3530,13 +4158,13 @@
       <c r="B8" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="152" t="n"/>
+      <c r="C8" s="159" t="n"/>
       <c r="D8" s="61" t="inlineStr">
         <is>
           <t>20% of production</t>
         </is>
       </c>
-      <c r="E8" s="123" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per 2-3 days</t>
         </is>
@@ -3544,12 +4172,12 @@
       <c r="F8" s="62" t="n">
         <v>20000</v>
       </c>
-      <c r="G8" s="123" t="inlineStr">
+      <c r="G8" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per 2-3 days</t>
         </is>
       </c>
-      <c r="H8" s="123" t="inlineStr">
+      <c r="H8" s="131" t="inlineStr">
         <is>
           <t>1 in 50</t>
         </is>
@@ -3565,13 +4193,13 @@
       <c r="B9" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="150" t="n"/>
+      <c r="C9" s="157" t="n"/>
       <c r="D9" s="61" t="inlineStr">
         <is>
           <t>10% of production</t>
         </is>
       </c>
-      <c r="E9" s="123" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per week</t>
         </is>
@@ -3579,12 +4207,12 @@
       <c r="F9" s="62" t="n">
         <v>10000</v>
       </c>
-      <c r="G9" s="123" t="inlineStr">
+      <c r="G9" s="131" t="inlineStr">
         <is>
           <t>&gt; 1 per week</t>
         </is>
       </c>
-      <c r="H9" s="123" t="inlineStr">
+      <c r="H9" s="131" t="inlineStr">
         <is>
           <t>1 in 100</t>
         </is>
@@ -3600,7 +4228,7 @@
       <c r="B10" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="123" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3610,7 +4238,7 @@
           <t>5% of production</t>
         </is>
       </c>
-      <c r="E10" s="123" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>1 per month</t>
         </is>
@@ -3618,12 +4246,12 @@
       <c r="F10" s="62" t="n">
         <v>5000</v>
       </c>
-      <c r="G10" s="123" t="inlineStr">
+      <c r="G10" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per 2 weeks</t>
         </is>
       </c>
-      <c r="H10" s="123" t="inlineStr">
+      <c r="H10" s="131" t="inlineStr">
         <is>
           <t>1 in 500</t>
         </is>
@@ -3639,13 +4267,13 @@
       <c r="B11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="152" t="n"/>
+      <c r="C11" s="159" t="n"/>
       <c r="D11" s="61" t="inlineStr">
         <is>
           <t>0.5% of production</t>
         </is>
       </c>
-      <c r="E11" s="123" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>2 per year</t>
         </is>
@@ -3653,12 +4281,12 @@
       <c r="F11" s="62" t="n">
         <v>1000</v>
       </c>
-      <c r="G11" s="123" t="inlineStr">
+      <c r="G11" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per quarter</t>
         </is>
       </c>
-      <c r="H11" s="123" t="inlineStr">
+      <c r="H11" s="131" t="inlineStr">
         <is>
           <t>1 in 2,000</t>
         </is>
@@ -3674,26 +4302,26 @@
       <c r="B12" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="150" t="n"/>
+      <c r="C12" s="157" t="n"/>
       <c r="D12" s="61" t="inlineStr">
         <is>
           <t>0.1% of production</t>
         </is>
       </c>
-      <c r="E12" s="123" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>1 per year</t>
         </is>
       </c>
-      <c r="F12" s="123" t="n">
+      <c r="F12" s="131" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="123" t="inlineStr">
+      <c r="G12" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per half year</t>
         </is>
       </c>
-      <c r="H12" s="123" t="inlineStr">
+      <c r="H12" s="131" t="inlineStr">
         <is>
           <t>1 in 10,000</t>
         </is>
@@ -3709,7 +4337,7 @@
       <c r="B13" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="123" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3719,20 +4347,20 @@
           <t>0.05% of production</t>
         </is>
       </c>
-      <c r="E13" s="123" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>1 per 5 years</t>
         </is>
       </c>
-      <c r="F13" s="123" t="n">
+      <c r="F13" s="131" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="123" t="inlineStr">
+      <c r="G13" s="131" t="inlineStr">
         <is>
           <t>&gt;1 per year</t>
         </is>
       </c>
-      <c r="H13" s="123" t="inlineStr">
+      <c r="H13" s="131" t="inlineStr">
         <is>
           <t>1 in 100,000</t>
         </is>
@@ -3748,26 +4376,26 @@
       <c r="B14" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="150" t="n"/>
+      <c r="C14" s="157" t="n"/>
       <c r="D14" s="61" t="inlineStr">
         <is>
           <t>0.01% of production</t>
         </is>
       </c>
-      <c r="E14" s="123" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>1 per 10 years</t>
         </is>
       </c>
-      <c r="F14" s="123" t="n">
+      <c r="F14" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="123" t="inlineStr">
+      <c r="G14" s="131" t="inlineStr">
         <is>
           <t>&lt;1 per year</t>
         </is>
       </c>
-      <c r="H14" s="123" t="inlineStr">
+      <c r="H14" s="131" t="inlineStr">
         <is>
           <t>1 in 1,000,000</t>
         </is>
@@ -3783,7 +4411,7 @@
       <c r="B15" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="123" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Very Low</t>
         </is>
@@ -3793,17 +4421,17 @@
           <t>Less than 0.01% of production</t>
         </is>
       </c>
-      <c r="E15" s="123" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>&lt;1 per 10 years</t>
         </is>
       </c>
-      <c r="F15" s="123" t="inlineStr">
+      <c r="F15" s="131" t="inlineStr">
         <is>
           <t>zero</t>
         </is>
       </c>
-      <c r="G15" s="123" t="inlineStr">
+      <c r="G15" s="131" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
@@ -3840,7 +4468,7 @@
       </c>
     </row>
     <row r="17" hidden="1">
-      <c r="B17" s="124" t="n"/>
+      <c r="B17" s="132" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="70" t="n"/>
@@ -3856,8 +4484,8 @@
       <c r="B20" s="71" t="n"/>
       <c r="C20" s="71" t="n"/>
       <c r="D20" s="72" t="n"/>
-      <c r="H20" s="125" t="n"/>
-      <c r="I20" s="125" t="n"/>
+      <c r="H20" s="133" t="n"/>
+      <c r="I20" s="133" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="71" t="n"/>
@@ -3878,9 +4506,9 @@
     <mergeCell ref="J3:J5"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B2:J2"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B17:I17"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="H20:I21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="These columns are not intended to &quot;equal&quot; one another, but serve as a reference that the cross functional team may use to rank process occurrence."/>
@@ -3933,73 +4561,73 @@
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
-      <c r="B2" s="147" t="inlineStr">
+      <c r="B2" s="154" t="inlineStr">
         <is>
           <t>PFMEA - Severity
 The team should agree on the criteria and ranking values. Select one way and consistently apply that scale.</t>
         </is>
       </c>
-      <c r="C2" s="148" t="n"/>
-      <c r="D2" s="148" t="n"/>
-      <c r="E2" s="148" t="n"/>
-      <c r="F2" s="148" t="n"/>
-      <c r="G2" s="149" t="n"/>
+      <c r="C2" s="155" t="n"/>
+      <c r="D2" s="155" t="n"/>
+      <c r="E2" s="155" t="n"/>
+      <c r="F2" s="155" t="n"/>
+      <c r="G2" s="156" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="132" t="inlineStr">
+      <c r="B3" s="134" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="134" t="inlineStr">
         <is>
           <t>Modified from J1739 / AS13004</t>
         </is>
       </c>
-      <c r="D3" s="148" t="n"/>
-      <c r="E3" s="148" t="n"/>
-      <c r="F3" s="149" t="n"/>
-      <c r="G3" s="122" t="inlineStr">
+      <c r="D3" s="155" t="n"/>
+      <c r="E3" s="155" t="n"/>
+      <c r="F3" s="156" t="n"/>
+      <c r="G3" s="124" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29.4" customHeight="1" thickBot="1">
-      <c r="B4" s="122" t="inlineStr">
+      <c r="B4" s="124" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-      <c r="C4" s="122" t="inlineStr">
+      <c r="C4" s="124" t="inlineStr">
         <is>
           <t>Severity of Effect on Product (Customer Effect)</t>
         </is>
       </c>
-      <c r="D4" s="122" t="inlineStr">
+      <c r="D4" s="124" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="E4" s="122" t="inlineStr">
+      <c r="E4" s="124" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F4" s="122" t="inlineStr">
+      <c r="F4" s="124" t="inlineStr">
         <is>
           <t>Severity of Effect on Process (Manufacturing / Assembly Effect)</t>
         </is>
       </c>
-      <c r="G4" s="150" t="n"/>
+      <c r="G4" s="157" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1" thickBot="1">
-      <c r="B5" s="123" t="inlineStr">
+      <c r="B5" s="131" t="inlineStr">
         <is>
           <t>Failure to meet safety and/or regulatory requirements</t>
         </is>
       </c>
-      <c r="C5" s="123" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Potential failure mode affects safe operation and/or involves noncompliance with regulations without warning</t>
         </is>
@@ -4007,12 +4635,12 @@
       <c r="D5" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="123" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Failure to meet safety and/or regulatory requirements</t>
         </is>
       </c>
-      <c r="F5" s="123" t="inlineStr">
+      <c r="F5" s="131" t="inlineStr">
         <is>
           <t>May endanger operator, machine or assembly without warning.</t>
         </is>
@@ -4020,8 +4648,8 @@
       <c r="G5" s="46" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1" thickBot="1">
-      <c r="B6" s="150" t="n"/>
-      <c r="C6" s="123" t="inlineStr">
+      <c r="B6" s="157" t="n"/>
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning</t>
         </is>
@@ -4029,8 +4657,8 @@
       <c r="D6" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="150" t="n"/>
-      <c r="F6" s="123" t="inlineStr">
+      <c r="E6" s="157" t="n"/>
+      <c r="F6" s="131" t="inlineStr">
         <is>
           <t>May endanger operator, machine or assembly with warning.</t>
         </is>
@@ -4038,12 +4666,12 @@
       <c r="G6" s="46" t="n"/>
     </row>
     <row r="7" ht="57.6" customHeight="1" thickBot="1">
-      <c r="B7" s="123" t="inlineStr">
+      <c r="B7" s="131" t="inlineStr">
         <is>
           <t>Loss or degradation of primary function</t>
         </is>
       </c>
-      <c r="C7" s="123" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Loss of primary function (product inoperable, does not affect safe operation)</t>
         </is>
@@ -4051,12 +4679,12 @@
       <c r="D7" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="123" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Major disruption</t>
         </is>
       </c>
-      <c r="F7" s="123" t="inlineStr">
+      <c r="F7" s="131" t="inlineStr">
         <is>
           <t>100% of product may have to be scrapped. Line shutdown or stop ship.</t>
         </is>
@@ -4064,8 +4692,8 @@
       <c r="G7" s="46" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" thickBot="1">
-      <c r="B8" s="150" t="n"/>
-      <c r="C8" s="123" t="inlineStr">
+      <c r="B8" s="157" t="n"/>
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Degradation of primary function (product operable, but at a reduced level of performance)</t>
         </is>
@@ -4073,12 +4701,12 @@
       <c r="D8" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="123" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Significant disruption</t>
         </is>
       </c>
-      <c r="F8" s="123" t="inlineStr">
+      <c r="F8" s="131" t="inlineStr">
         <is>
           <t>A portion of the production run may have to be scrapped. Deviation from primary process; decreased line speed or added manpower).</t>
         </is>
@@ -4086,12 +4714,12 @@
       <c r="G8" s="46" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" thickBot="1">
-      <c r="B9" s="123" t="inlineStr">
+      <c r="B9" s="131" t="inlineStr">
         <is>
           <t>Loss or degradation of secondary function</t>
         </is>
       </c>
-      <c r="C9" s="123" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">Loss of secondary function (product operable but service life greatly reduced, convenience item(s) inoperable, customer dissatisfied) </t>
         </is>
@@ -4099,12 +4727,12 @@
       <c r="D9" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="123" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Moderate disruption</t>
         </is>
       </c>
-      <c r="F9" s="123" t="inlineStr">
+      <c r="F9" s="131" t="inlineStr">
         <is>
           <t>100% of production run may have to be reworked off line and accepted</t>
         </is>
@@ -4112,8 +4740,8 @@
       <c r="G9" s="46" t="n"/>
     </row>
     <row r="10" ht="55.8" customHeight="1" thickBot="1">
-      <c r="B10" s="150" t="n"/>
-      <c r="C10" s="123" t="inlineStr">
+      <c r="B10" s="157" t="n"/>
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Degradation of secondary function (product operable but appearance affected, convenience item(s)  operable at a reduced level, customer dissatisfied.</t>
         </is>
@@ -4121,8 +4749,8 @@
       <c r="D10" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="150" t="n"/>
-      <c r="F10" s="123" t="inlineStr">
+      <c r="E10" s="157" t="n"/>
+      <c r="F10" s="131" t="inlineStr">
         <is>
           <t xml:space="preserve">A proportion of the production run may have to be reworked off line and acepted </t>
         </is>
@@ -4130,12 +4758,12 @@
       <c r="G10" s="46" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1" thickBot="1">
-      <c r="B11" s="123" t="inlineStr">
+      <c r="B11" s="131" t="inlineStr">
         <is>
           <t>Annoyance</t>
         </is>
       </c>
-      <c r="C11" s="123" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Appearance, fit and finish type items do not conform, defect noticed by most of the customers (&gt;75%)</t>
         </is>
@@ -4143,12 +4771,12 @@
       <c r="D11" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="123" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Moderate disruption</t>
         </is>
       </c>
-      <c r="F11" s="123" t="inlineStr">
+      <c r="F11" s="131" t="inlineStr">
         <is>
           <t>100% of production run may have to be reworked in station before it is processed.</t>
         </is>
@@ -4156,8 +4784,8 @@
       <c r="G11" s="46" t="n"/>
     </row>
     <row r="12" ht="42" customHeight="1" thickBot="1">
-      <c r="B12" s="152" t="n"/>
-      <c r="C12" s="123" t="inlineStr">
+      <c r="B12" s="159" t="n"/>
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>Appearance, fit and finish type items do not conform, defect noticed by about half of the customers (50%)</t>
         </is>
@@ -4165,8 +4793,8 @@
       <c r="D12" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="150" t="n"/>
-      <c r="F12" s="123" t="inlineStr">
+      <c r="E12" s="157" t="n"/>
+      <c r="F12" s="131" t="inlineStr">
         <is>
           <t>A proportion of the production run may have to be reworked in station before it is processed.</t>
         </is>
@@ -4174,8 +4802,8 @@
       <c r="G12" s="46" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1" thickBot="1">
-      <c r="B13" s="150" t="n"/>
-      <c r="C13" s="123" t="inlineStr">
+      <c r="B13" s="157" t="n"/>
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Appearance, fit and finish type items do not conform, defect noticed by discriminating customers (&lt;25%)</t>
         </is>
@@ -4183,12 +4811,12 @@
       <c r="D13" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="123" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Minor disruption</t>
         </is>
       </c>
-      <c r="F13" s="123" t="inlineStr">
+      <c r="F13" s="131" t="inlineStr">
         <is>
           <t>Slight inconvenience to process, operation or operator.</t>
         </is>
@@ -4196,12 +4824,12 @@
       <c r="G13" s="46" t="n"/>
     </row>
     <row r="14" ht="18.6" customHeight="1" thickBot="1">
-      <c r="B14" s="123" t="inlineStr">
+      <c r="B14" s="131" t="inlineStr">
         <is>
           <t>No effect</t>
         </is>
       </c>
-      <c r="C14" s="123" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>No discernible effect</t>
         </is>
@@ -4209,12 +4837,12 @@
       <c r="D14" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="123" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>No effect</t>
         </is>
       </c>
-      <c r="F14" s="123" t="inlineStr">
+      <c r="F14" s="131" t="inlineStr">
         <is>
           <t>No discernible effect</t>
         </is>
@@ -4295,44 +4923,44 @@
       <c r="B2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="153" t="inlineStr">
+      <c r="A3" s="160" t="inlineStr">
         <is>
           <t>1.  All provisions of Product Resources' ISO 9001 QMS apply and are implemented.</t>
         </is>
       </c>
-      <c r="B3" s="154" t="n"/>
+      <c r="B3" s="161" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="153" t="inlineStr">
+      <c r="A4" s="160" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B4" s="154" t="n"/>
+      <c r="B4" s="161" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="153" t="inlineStr">
+      <c r="A5" s="160" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B5" s="154" t="n"/>
+      <c r="B5" s="161" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="153" t="inlineStr">
+      <c r="A6" s="160" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B6" s="154" t="n"/>
+      <c r="B6" s="161" t="n"/>
     </row>
     <row r="7" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A7" s="155" t="inlineStr">
+      <c r="A7" s="162" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B7" s="156" t="n"/>
+      <c r="B7" s="163" t="n"/>
     </row>
     <row r="8" ht="14.4" customHeight="1" thickBot="1" thickTop="1">
       <c r="A8" s="5" t="n"/>

--- a/pfmea_audited.xlsx
+++ b/pfmea_audited.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1770" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1770" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PFMEA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="P-DET" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="P-OCC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="P-SEV" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Risk Classification Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PFMEA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Agent Benefits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="P-DET" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="P-OCC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="P-SEV" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PFMEA_Audited" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="CustCoC">'[1]Summary 1'!$R$41</definedName>
+    <definedName name="CustCoC">#REF!</definedName>
     <definedName name="d">#REF!</definedName>
     <definedName name="data">#REF!</definedName>
     <definedName name="_xlnm.Database">#REF!</definedName>
@@ -33,15 +33,18 @@
     <definedName name="Plage">#REF!</definedName>
     <definedName name="Sev">Assumptions!$B$10:$B$19</definedName>
     <definedName name="ww">TRUE</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'P-DET'!$A$1:$I$15</definedName>
-    <definedName name="d" localSheetId="3">#REF!</definedName>
-    <definedName name="data" localSheetId="3">#REF!</definedName>
-    <definedName name="_xlnm.Database" localSheetId="3">#REF!</definedName>
-    <definedName name="FF1_Programming" localSheetId="3">#REF!</definedName>
-    <definedName name="NEI_FF1" localSheetId="3">#REF!</definedName>
-    <definedName name="Overall" localSheetId="3">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'P-OCC'!$A$1:$K$17</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'P-SEV'!$A$1:$H$15</definedName>
+    <definedName name="Det" localSheetId="0">#REF!</definedName>
+    <definedName name="Occur" localSheetId="0">#REF!</definedName>
+    <definedName name="Sev" localSheetId="0">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'P-DET'!$A$1:$I$15</definedName>
+    <definedName name="d" localSheetId="5">#REF!</definedName>
+    <definedName name="data" localSheetId="5">#REF!</definedName>
+    <definedName name="_xlnm.Database" localSheetId="5">#REF!</definedName>
+    <definedName name="FF1_Programming" localSheetId="5">#REF!</definedName>
+    <definedName name="NEI_FF1" localSheetId="5">#REF!</definedName>
+    <definedName name="Overall" localSheetId="5">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'P-OCC'!$A$1:$K$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'P-SEV'!$A$1:$H$15</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -279,13 +282,23 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F1F1F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF1F1F1F"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00CC0000"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -382,8 +395,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -697,6 +716,266 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -706,11 +985,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -719,41 +1013,15 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -761,7 +1029,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -772,8 +1040,9 @@
       <alignment vertical="top"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1034,6 +1303,52 @@
     <xf numFmtId="0" fontId="21" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="28" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="32" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="37" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
@@ -1142,6 +1457,45 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -1223,6 +1577,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1236,60 +1602,62 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 23" xfId="2"/>
@@ -1297,6 +1665,7 @@
     <cellStyle name="Normal_DFMEA Explainit" xfId="4"/>
     <cellStyle name="Normal 3" xfId="5"/>
     <cellStyle name="Hyperlink 2" xfId="6"/>
+    <cellStyle name="Normal 4" xfId="7"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -1468,13 +1837,13 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
-      <col>16</col>
+      <col>19</col>
       <colOff>133350</colOff>
       <row>0</row>
       <rowOff>34637</rowOff>
     </from>
     <to>
-      <col>17</col>
+      <col>20</col>
       <colOff>327001</colOff>
       <row>2</row>
       <rowOff>132656</rowOff>
@@ -1518,7 +1887,7 @@
     </from>
     <to>
       <col>12</col>
-      <colOff>969466</colOff>
+      <colOff>742771</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
     </to>
@@ -1689,49 +2058,6 @@
     <clientData/>
   </twoCellAnchor>
 </wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Summary 1"/>
-      <sheetName val="Changes"/>
-      <sheetName val="MBO_Changes"/>
-      <sheetName val="Summary"/>
-      <sheetName val="Input"/>
-      <sheetName val="Output"/>
-      <sheetName val="8-bin"/>
-      <sheetName val="P&amp;L"/>
-      <sheetName val="Forex Anal"/>
-      <sheetName val="Exch"/>
-      <sheetName val="Plant Data"/>
-      <sheetName val="OEM-Engr-Product Data"/>
-      <sheetName val="Index"/>
-      <sheetName val="Instructions"/>
-      <sheetName val="Deviation"/>
-      <sheetName val="Change Record"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2035,6 +2361,1046 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="8.88671875" customWidth="1" style="86" min="1" max="16384"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="85" t="n"/>
+      <c r="B1" s="142" t="inlineStr">
+        <is>
+          <t>Severity Zone</t>
+        </is>
+      </c>
+      <c r="C1" s="174" t="n"/>
+      <c r="D1" s="174" t="n"/>
+      <c r="E1" s="174" t="n"/>
+      <c r="F1" s="174" t="n"/>
+      <c r="G1" s="174" t="n"/>
+      <c r="H1" s="174" t="n"/>
+      <c r="I1" s="174" t="n"/>
+      <c r="J1" s="174" t="n"/>
+      <c r="K1" s="174" t="n"/>
+      <c r="L1" s="175" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="87" t="n"/>
+      <c r="B2" s="88" t="n"/>
+      <c r="C2" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="88" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" s="88" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" s="88" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" s="89" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="143" t="inlineStr">
+        <is>
+          <t>Occurrence</t>
+        </is>
+      </c>
+      <c r="B3" s="94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="176" t="n"/>
+      <c r="B4" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="176" t="n"/>
+      <c r="B5" s="94" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A6" s="176" t="n"/>
+      <c r="B6" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A7" s="176" t="n"/>
+      <c r="B7" s="94" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="177" t="inlineStr">
+        <is>
+          <t>PRIORITY LEVEL</t>
+        </is>
+      </c>
+      <c r="P7" s="178" t="n"/>
+      <c r="Q7" s="178" t="n"/>
+      <c r="R7" s="178" t="n"/>
+      <c r="S7" s="179" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="176" t="n"/>
+      <c r="B8" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="137" t="inlineStr">
+        <is>
+          <t>Detection Zone</t>
+        </is>
+      </c>
+      <c r="P8" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" s="93" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="176" t="n"/>
+      <c r="B9" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="176" t="n"/>
+      <c r="P9" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="176" t="n"/>
+      <c r="B10" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="180" t="n"/>
+      <c r="P10" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="176" t="n"/>
+      <c r="B11" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="97" t="n"/>
+      <c r="P11" s="98" t="n"/>
+      <c r="Q11" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" s="95" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A12" s="180" t="n"/>
+      <c r="B12" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="91" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="99" t="n"/>
+      <c r="P12" s="100" t="n"/>
+      <c r="Q12" s="139" t="inlineStr">
+        <is>
+          <t>Severity Zone</t>
+        </is>
+      </c>
+      <c r="R12" s="181" t="n"/>
+      <c r="S12" s="182" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="97" t="n"/>
+      <c r="B13" s="98" t="n"/>
+      <c r="C13" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="94" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="94" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" s="95" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A14" s="99" t="n"/>
+      <c r="B14" s="100" t="n"/>
+      <c r="C14" s="139" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D14" s="181" t="n"/>
+      <c r="E14" s="181" t="n"/>
+      <c r="F14" s="181" t="n"/>
+      <c r="G14" s="181" t="n"/>
+      <c r="H14" s="181" t="n"/>
+      <c r="I14" s="181" t="n"/>
+      <c r="J14" s="181" t="n"/>
+      <c r="K14" s="181" t="n"/>
+      <c r="L14" s="182" t="n"/>
+    </row>
+    <row r="15" ht="13.8" customHeight="1" thickBot="1"/>
+    <row r="16">
+      <c r="A16" s="85" t="n"/>
+      <c r="B16" s="141" t="inlineStr">
+        <is>
+          <t>Detection Zone</t>
+        </is>
+      </c>
+      <c r="C16" s="174" t="n"/>
+      <c r="D16" s="174" t="n"/>
+      <c r="E16" s="174" t="n"/>
+      <c r="F16" s="174" t="n"/>
+      <c r="G16" s="174" t="n"/>
+      <c r="H16" s="174" t="n"/>
+      <c r="I16" s="174" t="n"/>
+      <c r="J16" s="174" t="n"/>
+      <c r="K16" s="174" t="n"/>
+      <c r="L16" s="183" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="87" t="n"/>
+      <c r="B17" s="88" t="n"/>
+      <c r="C17" s="88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="88" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="88" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="88" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="88" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" s="88" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" s="89" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="143" t="inlineStr">
+        <is>
+          <t>Detectopm</t>
+        </is>
+      </c>
+      <c r="B18" s="94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="176" t="n"/>
+      <c r="B19" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="176" t="n"/>
+      <c r="B20" s="94" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="176" t="n"/>
+      <c r="B21" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="176" t="n"/>
+      <c r="B22" s="94" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="176" t="n"/>
+      <c r="B23" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="176" t="n"/>
+      <c r="B24" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="176" t="n"/>
+      <c r="B25" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="176" t="n"/>
+      <c r="B26" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="L26" s="91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="180" t="n"/>
+      <c r="B27" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="L27" s="91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="97" t="n"/>
+      <c r="B28" s="98" t="n"/>
+      <c r="C28" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="94" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="94" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="94" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="94" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" s="94" t="n">
+        <v>9</v>
+      </c>
+      <c r="L28" s="95" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A29" s="99" t="n"/>
+      <c r="B29" s="100" t="n"/>
+      <c r="C29" s="139" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D29" s="181" t="n"/>
+      <c r="E29" s="181" t="n"/>
+      <c r="F29" s="181" t="n"/>
+      <c r="G29" s="181" t="n"/>
+      <c r="H29" s="181" t="n"/>
+      <c r="I29" s="181" t="n"/>
+      <c r="J29" s="181" t="n"/>
+      <c r="K29" s="181" t="n"/>
+      <c r="L29" s="182" t="n"/>
+    </row>
+    <row r="33" ht="35.4" customHeight="1"/>
+    <row r="34" ht="31.2" customHeight="1"/>
+    <row r="35" ht="46.8" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A18:A27"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="B16:L16"/>
+    <mergeCell ref="O7:S7"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="C14:L14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -2248,35 +3614,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="16.6640625" customWidth="1" min="1" max="1"/>
     <col width="25.6640625" customWidth="1" min="2" max="3"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="3.109375" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="7"/>
+    <col width="3.6640625" customWidth="1" min="5" max="5"/>
+    <col width="28.5546875" customWidth="1" min="6" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="5.44140625" customWidth="1" style="1" min="8" max="8"/>
-    <col width="15.6640625" customWidth="1" min="9" max="9"/>
+    <col width="23.33203125" customWidth="1" min="9" max="9"/>
     <col width="5.109375" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" style="1" min="11" max="11"/>
-    <col width="16.5546875" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" style="1" min="14" max="14"/>
-    <col width="3.109375" bestFit="1" customWidth="1" style="1" min="15" max="17"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" style="1" min="18" max="18"/>
+    <col width="5.6640625" customWidth="1" style="1" min="11" max="11"/>
+    <col width="19.6640625" customWidth="1" min="12" max="12"/>
+    <col width="11.77734375" customWidth="1" min="13" max="13"/>
+    <col width="13.44140625" customWidth="1" min="14" max="14"/>
+    <col width="13.109375" customWidth="1" min="15" max="15"/>
+    <col width="15.5546875" customWidth="1" min="16" max="16"/>
+    <col width="12.6640625" customWidth="1" style="1" min="17" max="17"/>
+    <col width="3.109375" bestFit="1" customWidth="1" style="1" min="18" max="20"/>
+    <col width="5" customWidth="1" style="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.6" customHeight="1">
-      <c r="A1" s="91" t="inlineStr">
+      <c r="A1" s="113" t="inlineStr">
         <is>
           <t>Quality Tools</t>
         </is>
@@ -2284,24 +3653,27 @@
       <c r="B1" s="19" t="n"/>
       <c r="C1" s="19" t="n"/>
       <c r="D1" s="18" t="n"/>
-      <c r="G1" s="18" t="n"/>
-      <c r="H1" s="34" t="inlineStr">
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="34" t="inlineStr">
         <is>
           <t>Process FMEA</t>
         </is>
       </c>
-      <c r="I1" s="34" t="n"/>
-      <c r="J1" s="18" t="n"/>
-      <c r="K1" s="19" t="n"/>
+      <c r="G1" s="34" t="n"/>
+      <c r="H1" s="18" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+      <c r="K1" s="18" t="n"/>
       <c r="L1" s="19" t="n"/>
-      <c r="O1" s="18" t="n"/>
-      <c r="R1" s="19" t="n"/>
-      <c r="S1" s="19" t="n"/>
+      <c r="M1" s="19" t="n"/>
+      <c r="N1" s="19" t="n"/>
+      <c r="O1" s="19" t="n"/>
+      <c r="P1" s="19" t="n"/>
+      <c r="Q1" s="18" t="n"/>
+      <c r="R1" s="18" t="n"/>
+      <c r="S1" s="18" t="n"/>
       <c r="T1" s="18" t="n"/>
       <c r="U1" s="18" t="n"/>
-      <c r="V1" s="18" t="n"/>
-      <c r="W1" s="18" t="n"/>
-      <c r="X1" s="18" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
@@ -2312,20 +3684,23 @@
       <c r="B2" s="19" t="n"/>
       <c r="C2" s="19" t="n"/>
       <c r="D2" s="18" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
       <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
+      <c r="H2" s="18" t="n"/>
       <c r="I2" s="19" t="n"/>
-      <c r="J2" s="18" t="n"/>
-      <c r="K2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="18" t="n"/>
       <c r="L2" s="19" t="n"/>
-      <c r="O2" s="18" t="n"/>
-      <c r="R2" s="19" t="n"/>
-      <c r="S2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="19" t="n"/>
+      <c r="Q2" s="18" t="n"/>
+      <c r="R2" s="18" t="n"/>
+      <c r="S2" s="18" t="n"/>
       <c r="T2" s="18" t="n"/>
       <c r="U2" s="18" t="n"/>
-      <c r="V2" s="18" t="n"/>
-      <c r="W2" s="18" t="n"/>
-      <c r="X2" s="18" t="n"/>
     </row>
     <row r="3" ht="13.8" customHeight="1" thickBot="1">
       <c r="A3" s="21" t="inlineStr">
@@ -2336,96 +3711,105 @@
       <c r="B3" s="22" t="n"/>
       <c r="C3" s="22" t="n"/>
       <c r="D3" s="18" t="n"/>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>Instructions</t>
         </is>
       </c>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
       <c r="H3" s="22" t="n"/>
       <c r="I3" s="22" t="n"/>
       <c r="J3" s="22" t="n"/>
-      <c r="K3" s="22" t="n"/>
-      <c r="L3" s="22" t="n"/>
-      <c r="O3" s="18" t="n"/>
-      <c r="R3" s="19" t="n"/>
-      <c r="S3" s="19" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="19" t="n"/>
+      <c r="M3" s="19" t="n"/>
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="19" t="n"/>
+      <c r="P3" s="19" t="n"/>
+      <c r="Q3" s="18" t="n"/>
+      <c r="R3" s="18" t="n"/>
+      <c r="S3" s="18" t="n"/>
       <c r="T3" s="18" t="n"/>
       <c r="U3" s="18" t="n"/>
-      <c r="V3" s="18" t="n"/>
-      <c r="W3" s="18" t="n"/>
-      <c r="X3" s="18" t="n"/>
     </row>
     <row r="4" ht="21" customHeight="1">
-      <c r="A4" s="100" t="inlineStr">
+      <c r="A4" s="122" t="inlineStr">
         <is>
           <t xml:space="preserve">This template is for use by Product Resources to record the Process Failure Mode and Effects Analysis (DFMEA) for medical and other devices.  FMEA is also referred to as Failure Modes, Effects, and Criticality Analysis (FMECA).  </t>
         </is>
       </c>
-      <c r="B4" s="139" t="n"/>
-      <c r="C4" s="139" t="n"/>
+      <c r="B4" s="184" t="n"/>
+      <c r="C4" s="184" t="n"/>
       <c r="D4" s="18" t="n"/>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H4" s="92" t="inlineStr">
+      <c r="F4" s="114" t="inlineStr">
         <is>
           <t>Please see the guidance in 90-2000-7.1 regarding FMEA process before beginning an FMEA</t>
         </is>
       </c>
-      <c r="I4" s="139" t="n"/>
-      <c r="J4" s="139" t="n"/>
-      <c r="K4" s="102" t="n"/>
-      <c r="L4" s="24" t="n"/>
-      <c r="O4" s="18" t="n"/>
-      <c r="R4" s="90" t="inlineStr">
+      <c r="G4" s="184" t="n"/>
+      <c r="H4" s="184" t="n"/>
+      <c r="I4" s="124" t="n"/>
+      <c r="J4" s="24" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="112" t="inlineStr">
         <is>
           <t>Parameters:</t>
         </is>
       </c>
-      <c r="S4" s="140" t="n"/>
-      <c r="T4" s="140" t="n"/>
-      <c r="U4" s="140" t="n"/>
-      <c r="V4" s="141" t="n"/>
-      <c r="W4" s="90" t="inlineStr">
+      <c r="M4" s="185" t="n"/>
+      <c r="N4" s="185" t="n"/>
+      <c r="O4" s="185" t="n"/>
+      <c r="P4" s="185" t="n"/>
+      <c r="Q4" s="185" t="n"/>
+      <c r="R4" s="185" t="n"/>
+      <c r="S4" s="186" t="n"/>
+      <c r="T4" s="112" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="X4" s="141" t="n"/>
+      <c r="U4" s="186" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="19" t="n"/>
       <c r="B5" s="19" t="n"/>
       <c r="C5" s="19" t="n"/>
       <c r="D5" s="25" t="n"/>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H5" s="102" t="inlineStr">
+      <c r="F5" s="124" t="inlineStr">
         <is>
           <t>Initiate action to reduce the RPN</t>
         </is>
       </c>
-      <c r="I5" s="19" t="n"/>
-      <c r="J5" s="19" t="n"/>
-      <c r="K5" s="102" t="n"/>
-      <c r="L5" s="24" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="R5" s="90" t="inlineStr">
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="124" t="n"/>
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="112" t="inlineStr">
         <is>
           <t>RPN triggering requiring mitigation action:</t>
         </is>
       </c>
-      <c r="S5" s="140" t="n"/>
-      <c r="T5" s="140" t="n"/>
-      <c r="U5" s="140" t="n"/>
-      <c r="V5" s="140" t="n"/>
-      <c r="W5" s="141" t="n"/>
-      <c r="X5" s="26" t="n">
+      <c r="M5" s="185" t="n"/>
+      <c r="N5" s="185" t="n"/>
+      <c r="O5" s="185" t="n"/>
+      <c r="P5" s="185" t="n"/>
+      <c r="Q5" s="185" t="n"/>
+      <c r="R5" s="185" t="n"/>
+      <c r="S5" s="185" t="n"/>
+      <c r="T5" s="186" t="n"/>
+      <c r="U5" s="26" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2434,58 +3818,64 @@
       <c r="B6" s="19" t="n"/>
       <c r="C6" s="19" t="n"/>
       <c r="D6" s="25" t="n"/>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="H6" s="102" t="inlineStr">
+      <c r="F6" s="124" t="inlineStr">
         <is>
           <t>Re-evaluate the RPN value after completion of the recommended actions</t>
         </is>
       </c>
-      <c r="I6" s="19" t="n"/>
-      <c r="J6" s="19" t="n"/>
-      <c r="K6" s="102" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="O6" s="18" t="n"/>
-      <c r="R6" s="90" t="inlineStr">
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="124" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="112" t="inlineStr">
         <is>
           <t>Severity (Sev) requiring mitigation action regardless of RPN:</t>
         </is>
       </c>
-      <c r="S6" s="140" t="n"/>
-      <c r="T6" s="140" t="n"/>
-      <c r="U6" s="140" t="n"/>
-      <c r="V6" s="140" t="n"/>
-      <c r="W6" s="141" t="n"/>
-      <c r="X6" s="26" t="n">
+      <c r="M6" s="185" t="n"/>
+      <c r="N6" s="185" t="n"/>
+      <c r="O6" s="185" t="n"/>
+      <c r="P6" s="185" t="n"/>
+      <c r="Q6" s="185" t="n"/>
+      <c r="R6" s="185" t="n"/>
+      <c r="S6" s="185" t="n"/>
+      <c r="T6" s="186" t="n"/>
+      <c r="U6" s="26" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="15.6" customHeight="1">
-      <c r="A7" s="89" t="inlineStr">
+      <c r="A7" s="111" t="inlineStr">
         <is>
           <t>PROCESS FAILURE MODE AND EFFECTS ANALYSIS (PFMEA)</t>
         </is>
       </c>
-      <c r="B7" s="140" t="n"/>
-      <c r="C7" s="140" t="n"/>
-      <c r="D7" s="140" t="n"/>
-      <c r="G7" s="140" t="n"/>
-      <c r="H7" s="140" t="n"/>
-      <c r="I7" s="140" t="n"/>
-      <c r="J7" s="140" t="n"/>
-      <c r="K7" s="140" t="n"/>
-      <c r="L7" s="140" t="n"/>
-      <c r="O7" s="140" t="n"/>
-      <c r="R7" s="140" t="n"/>
-      <c r="S7" s="140" t="n"/>
-      <c r="T7" s="140" t="n"/>
-      <c r="U7" s="140" t="n"/>
-      <c r="V7" s="140" t="n"/>
-      <c r="W7" s="140" t="n"/>
-      <c r="X7" s="141" t="n"/>
+      <c r="B7" s="185" t="n"/>
+      <c r="C7" s="185" t="n"/>
+      <c r="D7" s="185" t="n"/>
+      <c r="E7" s="185" t="n"/>
+      <c r="F7" s="185" t="n"/>
+      <c r="G7" s="185" t="n"/>
+      <c r="H7" s="185" t="n"/>
+      <c r="I7" s="185" t="n"/>
+      <c r="J7" s="185" t="n"/>
+      <c r="K7" s="185" t="n"/>
+      <c r="L7" s="185" t="n"/>
+      <c r="M7" s="185" t="n"/>
+      <c r="N7" s="185" t="n"/>
+      <c r="O7" s="185" t="n"/>
+      <c r="P7" s="185" t="n"/>
+      <c r="Q7" s="185" t="n"/>
+      <c r="R7" s="185" t="n"/>
+      <c r="S7" s="185" t="n"/>
+      <c r="T7" s="185" t="n"/>
+      <c r="U7" s="186" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
@@ -2493,43 +3883,46 @@
           <t>Item:</t>
         </is>
       </c>
-      <c r="B8" s="98" t="inlineStr">
+      <c r="B8" s="120" t="inlineStr">
         <is>
           <t>Wheel damper</t>
         </is>
       </c>
-      <c r="C8" s="140" t="n"/>
-      <c r="D8" s="141" t="n"/>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="108" t="inlineStr">
+      <c r="C8" s="185" t="n"/>
+      <c r="D8" s="186" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="130" t="inlineStr">
         <is>
           <t>Responsibility:</t>
         </is>
       </c>
-      <c r="I8" s="140" t="n"/>
-      <c r="J8" s="141" t="n"/>
-      <c r="K8" s="98" t="inlineStr">
+      <c r="G8" s="185" t="n"/>
+      <c r="H8" s="186" t="n"/>
+      <c r="I8" s="120" t="inlineStr">
         <is>
           <t>Donald Trump</t>
         </is>
       </c>
-      <c r="L8" s="140" t="n"/>
-      <c r="O8" s="141" t="n"/>
-      <c r="R8" s="28" t="n"/>
-      <c r="S8" s="27" t="inlineStr">
+      <c r="J8" s="185" t="n"/>
+      <c r="K8" s="186" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+      <c r="O8" s="28" t="n"/>
+      <c r="P8" s="27" t="inlineStr">
         <is>
           <t>FMEA number:</t>
         </is>
       </c>
-      <c r="T8" s="98" t="inlineStr">
+      <c r="Q8" s="120" t="inlineStr">
         <is>
           <t>Filename</t>
         </is>
       </c>
-      <c r="U8" s="140" t="n"/>
-      <c r="V8" s="140" t="n"/>
-      <c r="W8" s="140" t="n"/>
-      <c r="X8" s="141" t="n"/>
+      <c r="R8" s="185" t="n"/>
+      <c r="S8" s="185" t="n"/>
+      <c r="T8" s="185" t="n"/>
+      <c r="U8" s="186" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
@@ -2537,39 +3930,42 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="B9" s="98" t="inlineStr">
+      <c r="B9" s="120" t="inlineStr">
         <is>
           <t>Drive shaft</t>
         </is>
       </c>
-      <c r="C9" s="140" t="n"/>
-      <c r="D9" s="141" t="n"/>
-      <c r="G9" s="107" t="n"/>
-      <c r="H9" s="99" t="inlineStr">
+      <c r="C9" s="185" t="n"/>
+      <c r="D9" s="186" t="n"/>
+      <c r="E9" s="129" t="n"/>
+      <c r="F9" s="121" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="I9" s="140" t="n"/>
-      <c r="J9" s="141" t="n"/>
-      <c r="K9" s="98" t="inlineStr">
+      <c r="G9" s="185" t="n"/>
+      <c r="H9" s="186" t="n"/>
+      <c r="I9" s="120" t="inlineStr">
         <is>
           <t>Selva Jeyaseelan</t>
         </is>
       </c>
-      <c r="L9" s="140" t="n"/>
-      <c r="O9" s="141" t="n"/>
-      <c r="R9" s="28" t="n"/>
-      <c r="S9" s="27" t="inlineStr">
+      <c r="J9" s="185" t="n"/>
+      <c r="K9" s="186" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
+      <c r="P9" s="27" t="inlineStr">
         <is>
           <t>Page :</t>
         </is>
       </c>
-      <c r="T9" s="107" t="n"/>
-      <c r="U9" s="140" t="n"/>
-      <c r="V9" s="140" t="n"/>
-      <c r="W9" s="140" t="n"/>
-      <c r="X9" s="141" t="n"/>
+      <c r="Q9" s="129" t="n"/>
+      <c r="R9" s="185" t="n"/>
+      <c r="S9" s="185" t="n"/>
+      <c r="T9" s="185" t="n"/>
+      <c r="U9" s="186" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
@@ -2577,220 +3973,214 @@
           <t>Core Team:</t>
         </is>
       </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="B10" s="125" t="inlineStr">
         <is>
           <t>Sunder Pichai, Sam Altman, Selva Jeyaseelan</t>
         </is>
       </c>
-      <c r="C10" s="140" t="n"/>
-      <c r="D10" s="140" t="n"/>
-      <c r="G10" s="140" t="n"/>
-      <c r="H10" s="140" t="n"/>
-      <c r="I10" s="140" t="n"/>
-      <c r="J10" s="140" t="n"/>
-      <c r="K10" s="140" t="n"/>
-      <c r="L10" s="140" t="n"/>
-      <c r="O10" s="141" t="n"/>
-      <c r="R10" s="28" t="n"/>
-      <c r="S10" s="27" t="inlineStr">
+      <c r="C10" s="185" t="n"/>
+      <c r="D10" s="185" t="n"/>
+      <c r="E10" s="185" t="n"/>
+      <c r="F10" s="185" t="n"/>
+      <c r="G10" s="185" t="n"/>
+      <c r="H10" s="185" t="n"/>
+      <c r="I10" s="185" t="n"/>
+      <c r="J10" s="185" t="n"/>
+      <c r="K10" s="186" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="28" t="n"/>
+      <c r="O10" s="28" t="n"/>
+      <c r="P10" s="27" t="inlineStr">
         <is>
           <t>FMEA Date (Orig):</t>
         </is>
       </c>
-      <c r="T10" s="30" t="n">
+      <c r="Q10" s="30" t="n">
         <v>46270</v>
       </c>
-      <c r="U10" s="109" t="inlineStr">
+      <c r="R10" s="131" t="inlineStr">
         <is>
           <t>Rev:</t>
         </is>
       </c>
-      <c r="V10" s="141" t="n"/>
-      <c r="W10" s="110" t="n"/>
-      <c r="X10" s="141" t="n"/>
+      <c r="S10" s="186" t="n"/>
+      <c r="T10" s="132" t="n"/>
+      <c r="U10" s="186" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="28" t="n"/>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="31" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
       <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
+      <c r="H11" s="31" t="n"/>
       <c r="I11" s="28" t="n"/>
-      <c r="J11" s="31" t="n"/>
-      <c r="K11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="31" t="n"/>
       <c r="L11" s="28" t="n"/>
-      <c r="O11" s="31" t="n"/>
-      <c r="R11" s="28" t="n"/>
-      <c r="S11" s="27" t="inlineStr">
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="27" t="inlineStr">
         <is>
           <t>FMEA Date (Cur):</t>
         </is>
       </c>
-      <c r="T11" s="30" t="n">
+      <c r="Q11" s="30" t="n">
         <v>46270</v>
       </c>
-      <c r="U11" s="109" t="inlineStr">
+      <c r="R11" s="131" t="inlineStr">
         <is>
           <t>Rev:</t>
         </is>
       </c>
-      <c r="V11" s="141" t="n"/>
-      <c r="W11" s="110" t="n"/>
-      <c r="X11" s="141" t="n"/>
+      <c r="S11" s="186" t="n"/>
+      <c r="T11" s="132" t="n"/>
+      <c r="U11" s="186" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="142" t="inlineStr">
+      <c r="A12" s="187" t="inlineStr">
         <is>
           <t xml:space="preserve"> Process</t>
         </is>
       </c>
-      <c r="B12" s="85" t="inlineStr">
+      <c r="B12" s="107" t="inlineStr">
         <is>
           <t>Potential Failure Mode</t>
         </is>
       </c>
-      <c r="C12" s="85" t="inlineStr">
+      <c r="C12" s="107" t="inlineStr">
         <is>
           <t>Potential Effect(s) of Failure</t>
         </is>
       </c>
-      <c r="D12" s="95" t="inlineStr">
+      <c r="D12" s="117" t="inlineStr">
         <is>
           <t>Sev</t>
         </is>
       </c>
-      <c r="E12" s="143" t="inlineStr">
-        <is>
-          <t>pred sev</t>
-        </is>
-      </c>
-      <c r="F12" s="143" t="inlineStr">
-        <is>
-          <t>sev reasoning</t>
-        </is>
-      </c>
-      <c r="G12" s="95" t="inlineStr">
+      <c r="E12" s="117" t="inlineStr">
         <is>
           <t>Cls</t>
         </is>
       </c>
-      <c r="H12" s="85" t="inlineStr">
+      <c r="F12" s="107" t="inlineStr">
         <is>
           <t>Potential Cause(s)/ Mechanism(s) of Failure</t>
         </is>
       </c>
-      <c r="I12" s="85" t="inlineStr">
+      <c r="G12" s="107" t="inlineStr">
         <is>
           <t>Current 
 Process Prevention
 Controls</t>
         </is>
       </c>
-      <c r="J12" s="95" t="inlineStr">
+      <c r="H12" s="117" t="inlineStr">
         <is>
           <t>Occ</t>
         </is>
       </c>
-      <c r="K12" s="85" t="inlineStr">
+      <c r="I12" s="107" t="inlineStr">
         <is>
           <t>Current 
 Process Detection Controls
 Controls</t>
         </is>
       </c>
-      <c r="L12" s="95" t="inlineStr">
+      <c r="J12" s="117" t="inlineStr">
         <is>
           <t>Det</t>
         </is>
       </c>
-      <c r="M12" s="143" t="inlineStr">
-        <is>
-          <t>pred det</t>
-        </is>
-      </c>
-      <c r="N12" s="143" t="inlineStr">
-        <is>
-          <t>det reasoning</t>
-        </is>
-      </c>
-      <c r="O12" s="95" t="inlineStr">
+      <c r="K12" s="117" t="inlineStr">
         <is>
           <t>RPN</t>
         </is>
       </c>
-      <c r="P12" s="143" t="inlineStr">
-        <is>
-          <t>D-P gap</t>
-        </is>
-      </c>
-      <c r="R12" s="85" t="inlineStr">
+      <c r="L12" s="107" t="inlineStr">
         <is>
           <t>Recommended Action(s)</t>
         </is>
       </c>
-      <c r="S12" s="85" t="inlineStr">
+      <c r="M12" s="107" t="inlineStr">
+        <is>
+          <t>Severity Zone</t>
+        </is>
+      </c>
+      <c r="N12" s="107" t="inlineStr">
+        <is>
+          <t>Detection Zone</t>
+        </is>
+      </c>
+      <c r="O12" s="107" t="inlineStr">
+        <is>
+          <t>Priority Level</t>
+        </is>
+      </c>
+      <c r="P12" s="107" t="inlineStr">
         <is>
           <t>Responsibility and Target Completion Date</t>
         </is>
       </c>
-      <c r="T12" s="111" t="inlineStr">
+      <c r="Q12" s="133" t="inlineStr">
         <is>
           <t>Action Results</t>
         </is>
       </c>
-      <c r="U12" s="140" t="n"/>
-      <c r="V12" s="140" t="n"/>
-      <c r="W12" s="140" t="n"/>
-      <c r="X12" s="141" t="n"/>
+      <c r="R12" s="185" t="n"/>
+      <c r="S12" s="185" t="n"/>
+      <c r="T12" s="185" t="n"/>
+      <c r="U12" s="186" t="n"/>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="144" t="n"/>
-      <c r="B13" s="144" t="n"/>
-      <c r="C13" s="144" t="n"/>
-      <c r="D13" s="144" t="n"/>
-      <c r="E13" s="145" t="n"/>
-      <c r="F13" s="145" t="n"/>
-      <c r="G13" s="144" t="n"/>
-      <c r="H13" s="144" t="n"/>
-      <c r="I13" s="144" t="n"/>
-      <c r="J13" s="144" t="n"/>
-      <c r="K13" s="144" t="n"/>
-      <c r="L13" s="144" t="n"/>
-      <c r="M13" s="145" t="n"/>
-      <c r="N13" s="145" t="n"/>
-      <c r="O13" s="144" t="n"/>
-      <c r="P13" s="145" t="n"/>
-      <c r="R13" s="144" t="n"/>
-      <c r="S13" s="144" t="n"/>
-      <c r="T13" s="85" t="inlineStr">
+      <c r="A13" s="188" t="n"/>
+      <c r="B13" s="188" t="n"/>
+      <c r="C13" s="188" t="n"/>
+      <c r="D13" s="188" t="n"/>
+      <c r="E13" s="188" t="n"/>
+      <c r="F13" s="188" t="n"/>
+      <c r="G13" s="188" t="n"/>
+      <c r="H13" s="188" t="n"/>
+      <c r="I13" s="188" t="n"/>
+      <c r="J13" s="188" t="n"/>
+      <c r="K13" s="188" t="n"/>
+      <c r="L13" s="188" t="n"/>
+      <c r="M13" s="188" t="n"/>
+      <c r="N13" s="188" t="n"/>
+      <c r="O13" s="188" t="n"/>
+      <c r="P13" s="188" t="n"/>
+      <c r="Q13" s="107" t="inlineStr">
         <is>
           <t>Actions Taken</t>
         </is>
       </c>
-      <c r="U13" s="95" t="inlineStr">
+      <c r="R13" s="117" t="inlineStr">
         <is>
           <t>Sev</t>
         </is>
       </c>
-      <c r="V13" s="95" t="inlineStr">
+      <c r="S13" s="117" t="inlineStr">
         <is>
           <t>Occ</t>
         </is>
       </c>
-      <c r="W13" s="95" t="inlineStr">
+      <c r="T13" s="117" t="inlineStr">
         <is>
           <t>Det</t>
         </is>
       </c>
-      <c r="X13" s="95" t="inlineStr">
+      <c r="U13" s="117" t="inlineStr">
         <is>
           <t>RPN</t>
         </is>
       </c>
     </row>
     <row r="14" ht="92.40000000000001" customHeight="1">
-      <c r="A14" s="146" t="inlineStr">
+      <c r="A14" s="189" t="inlineStr">
         <is>
           <t>10. Grease plastic bearning</t>
         </is>
@@ -2810,68 +4200,57 @@
       <c r="D14" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="147" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="148" t="inlineStr">
-        <is>
-          <t>severity is correct</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Severity Test:Defect text matches AIAG standard</t>
         </is>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>Daily maintenace check sheet
 Preventive Maintenance
 Work instruction for grease refill</t>
         </is>
       </c>
-      <c r="J14" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="H14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Read switch to find the level of grease in the tank (2)
 Layer Process Audit (6)</t>
         </is>
       </c>
-      <c r="L14" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="147" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" s="148" t="inlineStr">
-        <is>
-          <t>detection controls text matches AIAG detection criteria</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="P14" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R14" s="13" t="n"/>
-      <c r="S14" s="13" t="n"/>
+      <c r="J14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="2">
+        <f>D14*H14*J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="n"/>
       <c r="T14" s="14" t="n"/>
-      <c r="U14" s="14" t="n"/>
-      <c r="V14" s="14" t="n"/>
-      <c r="W14" s="14" t="n"/>
-      <c r="X14" s="2">
-        <f>IF(O14*P14*Q14&gt;0,O14*P14*Q14,K14)</f>
+      <c r="U14" s="2">
+        <f>IF(R14*S14*T14&gt;0,R14*S14*T14,K14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="79.2" customHeight="1">
-      <c r="A15" s="150" t="n"/>
+      <c r="A15" s="190" t="n"/>
       <c r="B15" s="13" t="inlineStr">
         <is>
           <t>Less grease in the bearing</t>
@@ -2887,72 +4266,61 @@
       <c r="D15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="151" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="152" t="inlineStr">
-        <is>
-          <t>'Portion of production run may have to be scrapped' maps to AIAG 7. The stated severity 5 is an under-rating.</t>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Severity test: Lower severity choosen</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>Severity test: Lower severity choosen</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>Preventive maintenance
 Calibration of gage</t>
         </is>
       </c>
-      <c r="J15" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="H15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>First Off Approval (2)
 Layered Process Audit (6)
 Calibration report (6)</t>
         </is>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="J15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M15" s="151" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" s="152" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (5) does not exactly match Strongest Detection Extracted (2). Recommended Detection: 2</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="P15" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R15" s="13" t="n"/>
-      <c r="S15" s="13" t="n"/>
+      <c r="K15" s="2">
+        <f>D15*H15*J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" s="13" t="n"/>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="14" t="n"/>
+      <c r="S15" s="14" t="n"/>
       <c r="T15" s="14" t="n"/>
-      <c r="U15" s="14" t="n"/>
-      <c r="V15" s="14" t="n"/>
-      <c r="W15" s="14" t="n"/>
-      <c r="X15" s="2">
-        <f>IF(O15*P15*Q15&gt;0,O15*P15*Q15,K15)</f>
+      <c r="U15" s="2">
+        <f>IF(R15*S15*T15&gt;0,R15*S15*T15,K15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="118.8" customHeight="1">
-      <c r="A16" s="144" t="n"/>
+      <c r="A16" s="188" t="n"/>
       <c r="B16" s="15" t="inlineStr">
         <is>
           <t>More grease in the bearning</t>
@@ -2967,64 +4335,53 @@
       <c r="D16" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="E16" s="147" t="n">
-        <v>9</v>
-      </c>
-      <c r="F16" s="148" t="inlineStr">
-        <is>
-          <t>severity is correct</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Severity Test:Defect text matches AIAG standard</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>Daily maintenace check sheet
 Preventive Maintenance
 Work instruction for grease refill</t>
         </is>
       </c>
-      <c r="J16" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>First Off Approval (2)
 Layered Process Audit (6)
 Calibration report (6)</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="J16" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="151" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" s="152" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (5) does not exactly match Strongest Detection Extracted (2). Recommended Detection: 2</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="P16" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R16" s="13" t="n"/>
-      <c r="S16" s="13" t="n"/>
+      <c r="K16" s="2">
+        <f>D16*H16*J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n"/>
       <c r="T16" s="14" t="n"/>
-      <c r="U16" s="14" t="n"/>
-      <c r="V16" s="14" t="n"/>
-      <c r="W16" s="14" t="n"/>
-      <c r="X16" s="2">
-        <f>IF(O16*P16*Q16&gt;0,O16*P16*Q16,K16)</f>
+      <c r="U16" s="2">
+        <f>IF(R16*S16*T16&gt;0,R16*S16*T16,K16)</f>
         <v/>
       </c>
     </row>
@@ -3040,64 +4397,53 @@
       <c r="D17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="151" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="152" t="inlineStr">
-        <is>
-          <t>"A proportion of the production run may have to be reworked off line and accepted" maps to AIAG severity 6. The stated severity 5 is an under-rating.</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>Severity test scenario: perfect match</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>Detection test scenario: Severe Semantic Mismatch (Over-rating)</t>
         </is>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>"Random visual inspection by supervisor once a shift (3)"</t>
+        </is>
+      </c>
       <c r="J17" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>"Random visual inspection by supervisor once a shift (3)"</t>
-        </is>
-      </c>
-      <c r="L17" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="151" t="n">
-        <v>9</v>
-      </c>
-      <c r="N17" s="152" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. Check 2 failed: "Random visual inspection by supervisor once a shift (3)" describes a weak random audit/visual inspection, not AIAG detection level 3. Recommended Detection: 9</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="P17" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R17" s="13" t="n"/>
-      <c r="S17" s="13" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K17" s="2">
+        <f>D17*H17*J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="14" t="n"/>
+      <c r="S17" s="14" t="n"/>
       <c r="T17" s="14" t="n"/>
-      <c r="U17" s="14" t="n"/>
-      <c r="V17" s="14" t="n"/>
-      <c r="W17" s="14" t="n"/>
-      <c r="X17" s="2">
-        <f>IF(O17*P17*Q17&gt;0,O17*P17*Q17,K17)</f>
+      <c r="U17" s="2">
+        <f>IF(R17*S17*T17&gt;0,R17*S17*T17,K17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="79.2" customHeight="1">
+    <row r="18" ht="52.8" customHeight="1">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="13" t="n"/>
       <c r="C18" s="13" t="inlineStr">
@@ -3108,60 +4454,49 @@
       <c r="D18" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="147" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="148" t="inlineStr">
-        <is>
-          <t>severity is correct</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Severity test scenario: Spelling and typo</t>
         </is>
       </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Severe Semantic Mismatch (Under-rating)</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>Detection test scenario: Severe Semantic Mismatch (Under-rating)</t>
+          <t>"In-station automated vision system that locks the machine if a defect is found (8)"</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>"In-station automated vision system that locks the machine if a defect is found (8)"</t>
-        </is>
-      </c>
-      <c r="L18" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="M18" s="151" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="152" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. The text describes in-station automated lock/stop control, which aligns to AIAG 3, not 8. Recommended Detection: 3</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="P18" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R18" s="13" t="n"/>
-      <c r="S18" s="13" t="n"/>
+      <c r="K18" s="2">
+        <f>D18*H18*J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
       <c r="T18" s="14" t="n"/>
-      <c r="U18" s="14" t="n"/>
-      <c r="V18" s="14" t="n"/>
-      <c r="W18" s="14" t="n"/>
-      <c r="X18" s="2">
-        <f>IF(O18*P18*Q18&gt;0,O18*P18*Q18,K18)</f>
+      <c r="U18" s="2">
+        <f>IF(R18*S18*T18&gt;0,R18*S18*T18,K18)</f>
         <v/>
       </c>
     </row>
@@ -3177,64 +4512,53 @@
       <c r="D19" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="151" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="152" t="inlineStr">
-        <is>
-          <t>'100% of product may have to be scrapped. Line shutdown or stop ship.' maps to AIAG 8, which is higher than the stated severity 7.</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Severity test scenario: Column Mismatch (Under-reporting)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Detection test scenario: Heavy Typographical Errors</t>
         </is>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>"Aoutmated varible gaging with red light buzer to notfy opreator (5)"</t>
+        </is>
+      </c>
       <c r="J19" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>"Aoutmated varible gaging with red light buzer to notfy opreator (5)"</t>
-        </is>
-      </c>
-      <c r="L19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="147" t="n">
-        <v>5</v>
-      </c>
-      <c r="N19" s="148" t="inlineStr">
-        <is>
-          <t>detection controls text matches AIAG detection criteria</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="P19" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
+      <c r="K19" s="2">
+        <f>D19*H19*J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="14" t="n"/>
+      <c r="S19" s="14" t="n"/>
       <c r="T19" s="14" t="n"/>
-      <c r="U19" s="14" t="n"/>
-      <c r="V19" s="14" t="n"/>
-      <c r="W19" s="14" t="n"/>
-      <c r="X19" s="2">
-        <f>IF(O19*P19*Q19&gt;0,O19*P19*Q19,K19)</f>
+      <c r="U19" s="2">
+        <f>IF(R19*S19*T19&gt;0,R19*S19*T19,K19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="66" customHeight="1">
+    <row r="20" ht="52.8" customHeight="1">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="13" t="n"/>
       <c r="C20" s="13" t="inlineStr">
@@ -3245,129 +4569,106 @@
       <c r="D20" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="151" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="152" t="inlineStr">
-        <is>
-          <t>'Loss of primary function' maps to AIAG 8. The stated 4 is an under-rating.</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Severity test scenario: EU: Loss of primary function (product inoperable, does not affect safe operation) (4)</t>
         </is>
       </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: . Multiple Controls (Stated matches Strongest)</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>5</v>
+      </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>Detection test scenario: . Multiple Controls (Stated matches Strongest)</t>
+          <t>"Visual check by operator (8)  Automated laser interlock in-station (3)"</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>"Visual check by operator (8)  Automated laser interlock in-station (3)"</t>
-        </is>
-      </c>
-      <c r="L20" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" s="147" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" s="148" t="inlineStr">
-        <is>
-          <t>detection controls text matches AIAG detection criteria</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="P20" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R20" s="13" t="n"/>
-      <c r="S20" s="13" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="K20" s="2">
+        <f>D20*H20*J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="n"/>
       <c r="T20" s="14" t="n"/>
-      <c r="U20" s="14" t="n"/>
-      <c r="V20" s="14" t="n"/>
-      <c r="W20" s="14" t="n"/>
-      <c r="X20" s="2">
-        <f>IF(O20*P20*Q20&gt;0,O20*P20*Q20,K20)</f>
+      <c r="U20" s="2">
+        <f>IF(R20*S20*T20&gt;0,R20*S20*T20,K20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="118.8" customHeight="1">
+    <row r="21" ht="39.6" customHeight="1">
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="13" t="n"/>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
-OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+          <t>S: Reduced performance</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="147" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="148" t="inlineStr">
-        <is>
-          <t>severity is correct</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>DFMEA PFMEA Gap analysis check</t>
-        </is>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>Severity: Irrelevant text</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Multiple Controls (Stated matches Weakest)</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>Detection test scenario: Multiple Controls (Stated matches Weakest)</t>
+          <t>"Visual check by operator (8) \n Automated laser interlock in-station (3)"</t>
         </is>
       </c>
       <c r="J21" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>"Visual check by operator (8) \n Automated laser interlock in-station (3)"</t>
-        </is>
-      </c>
-      <c r="L21" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="M21" s="151" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" s="152" t="inlineStr">
-        <is>
-          <t>detection controls text keywords do not match AIAG detection criteria. Check 1 failed: Original Stated Detection (8) does not exactly match Strongest Detection Extracted (3). Recommended Detection: 3</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>216</v>
-      </c>
-      <c r="P21" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R21" s="13" t="n"/>
-      <c r="S21" s="13" t="n"/>
+      <c r="K21" s="2">
+        <f>D21*H21*J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="14" t="n"/>
+      <c r="R21" s="14" t="n"/>
+      <c r="S21" s="14" t="n"/>
       <c r="T21" s="14" t="n"/>
-      <c r="U21" s="14" t="n"/>
-      <c r="V21" s="14" t="n"/>
-      <c r="W21" s="14" t="n"/>
-      <c r="X21" s="2">
-        <f>IF(O21*P21*Q21&gt;0,O21*P21*Q21,K21)</f>
+      <c r="U21" s="2">
+        <f>IF(R21*S21*T21&gt;0,R21*S21*T21,K21)</f>
         <v/>
       </c>
     </row>
@@ -3383,60 +4684,49 @@
       <c r="D22" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="E22" s="151" t="n">
-        <v>9</v>
-      </c>
-      <c r="F22" s="152" t="inlineStr">
-        <is>
-          <t>'Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning' maps to AIAG 9, which is the highest effect described.</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>DFMEA PFMEA Gap analysis check</t>
         </is>
       </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Missing Brackets / Parentheses</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>8</v>
+      </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>Detection test scenario: Missing Brackets / Parentheses</t>
+          <t>"Manual attribute go/no-go gauging in station 7"</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>"Manual attribute go/no-go gauging in station 7"</t>
-        </is>
-      </c>
-      <c r="L22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="M22" s="147" t="n">
-        <v>7</v>
-      </c>
-      <c r="N22" s="148" t="inlineStr">
-        <is>
-          <t>detection controls text matches AIAG detection criteria</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>504</v>
-      </c>
-      <c r="P22" s="153" t="inlineStr">
-        <is>
-          <t>Gap identified. Det must be &lt;3</t>
-        </is>
-      </c>
-      <c r="R22" s="13" t="n"/>
-      <c r="S22" s="13" t="n"/>
+      <c r="K22" s="2">
+        <f>D22*H22*J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" s="13" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="14" t="n"/>
+      <c r="S22" s="14" t="n"/>
       <c r="T22" s="14" t="n"/>
-      <c r="U22" s="14" t="n"/>
-      <c r="V22" s="14" t="n"/>
-      <c r="W22" s="14" t="n"/>
-      <c r="X22" s="2">
-        <f>IF(O22*P22*Q22&gt;0,O22*P22*Q22,K22)</f>
+      <c r="U22" s="2">
+        <f>IF(R22*S22*T22&gt;0,R22*S22*T22,K22)</f>
         <v/>
       </c>
     </row>
@@ -3453,110 +4743,98 @@
       <c r="D23" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="E23" s="147" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="148" t="inlineStr">
-        <is>
-          <t>severity is correct</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Severity Test:Defect text matches AIAG standard</t>
         </is>
       </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Number Confusions (Scores mixed with specs)</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>2</v>
+      </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>Detection test scenario: Number Confusions (Scores mixed with specs)</t>
+          <t>"Check 5 times a day using a 2 mm variable gauge (6)"`</t>
         </is>
       </c>
       <c r="J23" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>"Check 5 times a day using a 2 mm variable gauge (6)"`</t>
-        </is>
-      </c>
-      <c r="L23" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M23" s="147" t="n">
-        <v>6</v>
-      </c>
-      <c r="N23" s="148" t="inlineStr">
-        <is>
-          <t>detection controls text matches AIAG detection criteria</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="P23" s="149" t="inlineStr">
-        <is>
-          <t>no gap</t>
-        </is>
-      </c>
-      <c r="R23" s="13" t="n"/>
-      <c r="S23" s="13" t="n"/>
+      <c r="K23" s="2">
+        <f>D23*H23*J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P23" s="13" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="14" t="n"/>
+      <c r="S23" s="14" t="n"/>
       <c r="T23" s="14" t="n"/>
-      <c r="U23" s="14" t="n"/>
-      <c r="V23" s="14" t="n"/>
-      <c r="W23" s="14" t="n"/>
-      <c r="X23" s="2">
-        <f>IF(O23*P23*Q23&gt;0,O23*P23*Q23,K23)</f>
+      <c r="U23" s="2">
+        <f>IF(R23*S23*T23&gt;0,R23*S23*T23,K23)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="R6:W6"/>
-    <mergeCell ref="A7:X7"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="0" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="41">
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="Q12:U12"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="W10:X10"/>
+    <mergeCell ref="A7:U7"/>
     <mergeCell ref="B8:D8"/>
+    <mergeCell ref="R11:S11"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L5:T5"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="R10:S10"/>
     <mergeCell ref="N12:N13"/>
-    <mergeCell ref="K9:O9"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="Q8:U8"/>
+    <mergeCell ref="T10:U10"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="R12:R13"/>
-    <mergeCell ref="U11:V11"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I8:K8"/>
     <mergeCell ref="K12:K13"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="M12:M13"/>
     <mergeCell ref="O12:O13"/>
     <mergeCell ref="D12:D13"/>
-    <mergeCell ref="T9:X9"/>
-    <mergeCell ref="T12:X12"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K8:O8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="L6:T6"/>
+    <mergeCell ref="L4:S4"/>
+    <mergeCell ref="T11:U11"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="R5:W5"/>
-    <mergeCell ref="B10:O10"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="A4:C6"/>
     <mergeCell ref="P12:P13"/>
-    <mergeCell ref="T8:X8"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="Q9:U9"/>
+    <mergeCell ref="F6:H6"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="W11:X11"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="S12:S13"/>
-    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="B10:K10"/>
   </mergeCells>
-  <conditionalFormatting sqref="D14:D23 R14:R23">
+  <conditionalFormatting sqref="D14:D23 U14:U23">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>#REF!</formula>
     </cfRule>
@@ -3566,19 +4844,19 @@
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O14:O23">
+  <conditionalFormatting sqref="R14:R23">
     <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="D14:D23 O14:O23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D14:D23 R14:R23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Sev</formula1>
     </dataValidation>
-    <dataValidation sqref="H14:H23 P14:P23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H14:H23 S14:S23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Occur</formula1>
     </dataValidation>
-    <dataValidation sqref="J14:J23 Q14:Q23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J14:J23 T14:T23" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Det</formula1>
     </dataValidation>
   </dataValidations>
@@ -3588,7 +4866,306 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="C2:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="56.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="16.21875" bestFit="1" customWidth="1" min="4" max="5"/>
+    <col width="54.44140625" bestFit="1" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="C2" s="105" t="inlineStr">
+        <is>
+          <t>PFMEA Review steps</t>
+        </is>
+      </c>
+      <c r="D2" s="106" t="inlineStr">
+        <is>
+          <t>Current Process</t>
+        </is>
+      </c>
+      <c r="E2" s="106" t="inlineStr">
+        <is>
+          <t>New Process</t>
+        </is>
+      </c>
+      <c r="F2" s="106" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="103" t="inlineStr">
+        <is>
+          <t>Map the process step with failure mode</t>
+        </is>
+      </c>
+      <c r="D3" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E3" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="F3" s="103" t="inlineStr">
+        <is>
+          <t>Need Contextual information about part &amp; manufacturing process</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="103" t="inlineStr">
+        <is>
+          <t>Map the failure mode with effect of failure(s)</t>
+        </is>
+      </c>
+      <c r="D4" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E4" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="F4" s="103" t="inlineStr">
+        <is>
+          <t>Need Contextual information about part &amp; manufacturing process</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="103" t="inlineStr">
+        <is>
+          <t>Verify severity for different effect(s) of failure using AIAG standard</t>
+        </is>
+      </c>
+      <c r="D5" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E5" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F5" s="104" t="n"/>
+    </row>
+    <row r="6">
+      <c r="C6" s="103" t="inlineStr">
+        <is>
+          <t>Select the most severe effect of failure</t>
+        </is>
+      </c>
+      <c r="D6" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E6" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="F6" s="103" t="inlineStr">
+        <is>
+          <t>Need Contextual information about part &amp; manufacturing process</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="103" t="inlineStr">
+        <is>
+          <t>Verify cause of failure</t>
+        </is>
+      </c>
+      <c r="D7" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E7" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="F7" s="103" t="inlineStr">
+        <is>
+          <t>Need Contextual information about part &amp; manufacturing process</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="103" t="inlineStr">
+        <is>
+          <t>Verify prevention controls</t>
+        </is>
+      </c>
+      <c r="D8" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E8" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="F8" s="103" t="inlineStr">
+        <is>
+          <t>Need Contextual information about part &amp; manufacturing process</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="103" t="inlineStr">
+        <is>
+          <t>Verify Occurrence score using AIAG standard</t>
+        </is>
+      </c>
+      <c r="D9" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E9" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="F9" s="103" t="inlineStr">
+        <is>
+          <t>Need Contextual information about part &amp; manufacturing process</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="103" t="inlineStr">
+        <is>
+          <t>Verify detection for different detection contrls using AIAG standard</t>
+        </is>
+      </c>
+      <c r="D10" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E10" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F10" s="104" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="103" t="inlineStr">
+        <is>
+          <t>Verify severity zone Risk Classification Sheet</t>
+        </is>
+      </c>
+      <c r="D11" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E11" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F11" s="104" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="103" t="inlineStr">
+        <is>
+          <t>Verify detection zone using Risk Classification Sheet</t>
+        </is>
+      </c>
+      <c r="D12" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E12" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F12" s="104" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="103" t="inlineStr">
+        <is>
+          <t>Verify Risk Priority using Risk Classification Sheet</t>
+        </is>
+      </c>
+      <c r="D13" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E13" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F13" s="104" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="103" t="inlineStr">
+        <is>
+          <t>Perform DFMEA PFMEA gap analysis</t>
+        </is>
+      </c>
+      <c r="D14" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E14" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F14" s="104" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="103" t="inlineStr">
+        <is>
+          <t>Verify detection scores for Significant and Critical dimensions</t>
+        </is>
+      </c>
+      <c r="D15" s="103" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E15" s="103" t="inlineStr">
+        <is>
+          <t>LLM verification</t>
+        </is>
+      </c>
+      <c r="F15" s="104" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF99CCFF"/>
@@ -3618,48 +5195,48 @@
       </c>
     </row>
     <row r="2" ht="39" customHeight="1" thickBot="1">
-      <c r="B2" s="154" t="inlineStr">
+      <c r="B2" s="191" t="inlineStr">
         <is>
           <t>PFMEA - Detection
 The team should agree on the criteria and ranking values. Select one way and consistently apply that scale.</t>
         </is>
       </c>
-      <c r="C2" s="155" t="n"/>
-      <c r="D2" s="155" t="n"/>
-      <c r="E2" s="155" t="n"/>
-      <c r="F2" s="155" t="n"/>
-      <c r="G2" s="155" t="n"/>
-      <c r="H2" s="156" t="n"/>
+      <c r="C2" s="178" t="n"/>
+      <c r="D2" s="178" t="n"/>
+      <c r="E2" s="178" t="n"/>
+      <c r="F2" s="178" t="n"/>
+      <c r="G2" s="178" t="n"/>
+      <c r="H2" s="179" t="n"/>
       <c r="I2" s="74" t="n"/>
     </row>
     <row r="3" ht="18.6" customHeight="1" thickBot="1">
-      <c r="B3" s="134" t="inlineStr">
+      <c r="B3" s="169" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="C3" s="134" t="inlineStr">
+      <c r="C3" s="169" t="inlineStr">
         <is>
           <t>Modified from J1739 / AS13004</t>
         </is>
       </c>
-      <c r="D3" s="156" t="n"/>
-      <c r="E3" s="124" t="inlineStr">
+      <c r="D3" s="179" t="n"/>
+      <c r="E3" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve"> Mistake-proofed</t>
         </is>
       </c>
-      <c r="F3" s="124" t="inlineStr">
+      <c r="F3" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve"> Gauged</t>
         </is>
       </c>
-      <c r="G3" s="124" t="inlineStr">
+      <c r="G3" s="159" t="inlineStr">
         <is>
           <t xml:space="preserve"> Manual Inspection  </t>
         </is>
       </c>
-      <c r="H3" s="124" t="inlineStr">
+      <c r="H3" s="159" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
@@ -3667,25 +5244,25 @@
       <c r="I3" s="74" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1" thickBot="1">
-      <c r="B4" s="124" t="inlineStr">
+      <c r="B4" s="159" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="C4" s="124" t="inlineStr">
+      <c r="C4" s="159" t="inlineStr">
         <is>
           <t>Likelihood of Detection by Process Control - Category</t>
         </is>
       </c>
-      <c r="D4" s="124" t="inlineStr">
+      <c r="D4" s="159" t="inlineStr">
         <is>
           <t>Likelihood of Detection by Process Control - Criteria</t>
         </is>
       </c>
-      <c r="E4" s="157" t="n"/>
-      <c r="F4" s="157" t="n"/>
-      <c r="G4" s="157" t="n"/>
-      <c r="H4" s="157" t="n"/>
+      <c r="E4" s="192" t="n"/>
+      <c r="F4" s="192" t="n"/>
+      <c r="G4" s="192" t="n"/>
+      <c r="H4" s="192" t="n"/>
       <c r="K4" s="75" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1" thickBot="1">
@@ -3704,7 +5281,7 @@
       </c>
       <c r="E5" s="77" t="n"/>
       <c r="F5" s="78" t="n"/>
-      <c r="G5" s="158" t="inlineStr">
+      <c r="G5" s="193" t="inlineStr">
         <is>
           <t xml:space="preserve">100% Human Inspection </t>
         </is>
@@ -3727,7 +5304,7 @@
       </c>
       <c r="E6" s="80" t="n"/>
       <c r="F6" s="78" t="n"/>
-      <c r="G6" s="159" t="n"/>
+      <c r="G6" s="194" t="n"/>
       <c r="H6" s="79" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1" thickBot="1">
@@ -3746,7 +5323,7 @@
       </c>
       <c r="E7" s="80" t="n"/>
       <c r="F7" s="78" t="n"/>
-      <c r="G7" s="159" t="n"/>
+      <c r="G7" s="194" t="n"/>
       <c r="H7" s="79" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" thickBot="1">
@@ -3764,12 +5341,12 @@
         </is>
       </c>
       <c r="E8" s="80" t="n"/>
-      <c r="F8" s="158" t="inlineStr">
+      <c r="F8" s="193" t="inlineStr">
         <is>
           <t>Manual gauging is used on every part</t>
         </is>
       </c>
-      <c r="G8" s="159" t="n"/>
+      <c r="G8" s="194" t="n"/>
       <c r="H8" s="79" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" thickBot="1">
@@ -3787,8 +5364,8 @@
         </is>
       </c>
       <c r="E9" s="80" t="n"/>
-      <c r="F9" s="157" t="n"/>
-      <c r="G9" s="159" t="n"/>
+      <c r="F9" s="192" t="n"/>
+      <c r="G9" s="194" t="n"/>
       <c r="H9" s="79" t="n"/>
     </row>
     <row r="10" ht="58.5" customHeight="1" thickBot="1">
@@ -3806,12 +5383,12 @@
         </is>
       </c>
       <c r="E10" s="80" t="n"/>
-      <c r="F10" s="158" t="inlineStr">
+      <c r="F10" s="193" t="inlineStr">
         <is>
           <t>Automatic gauging or controls to detect discrepant part</t>
         </is>
       </c>
-      <c r="G10" s="157" t="n"/>
+      <c r="G10" s="192" t="n"/>
       <c r="H10" s="79" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1" thickBot="1">
@@ -3828,12 +5405,12 @@
           <t>Defect (Failure Mode) detection post-processing by automated controls that will detect discrepant part and lock part to prevent further processing.</t>
         </is>
       </c>
-      <c r="E11" s="158" t="inlineStr">
+      <c r="E11" s="193" t="inlineStr">
         <is>
           <t>Controls in place for mistake proofing the assembly</t>
         </is>
       </c>
-      <c r="F11" s="159" t="n"/>
+      <c r="F11" s="194" t="n"/>
       <c r="G11" s="81" t="n"/>
       <c r="H11" s="79" t="n"/>
     </row>
@@ -3851,8 +5428,8 @@
           <t>Defect (Failure Mode) detection in-station by automated controls that will detect discrepant part and automatically lock part in station to prevent further processing.</t>
         </is>
       </c>
-      <c r="E12" s="159" t="n"/>
-      <c r="F12" s="157" t="n"/>
+      <c r="E12" s="194" t="n"/>
+      <c r="F12" s="192" t="n"/>
       <c r="G12" s="81" t="n"/>
       <c r="H12" s="79" t="n"/>
     </row>
@@ -3870,7 +5447,7 @@
           <t>Error (Cause) detection in-station by automated controls that will detect error and prevent discrepant part from being made.</t>
         </is>
       </c>
-      <c r="E13" s="159" t="n"/>
+      <c r="E13" s="194" t="n"/>
       <c r="F13" s="78" t="n"/>
       <c r="G13" s="81" t="n"/>
       <c r="H13" s="79" t="n"/>
@@ -3889,7 +5466,7 @@
           <t>Error (Cause) prevention as a result of fixture design, machine design or part design.</t>
         </is>
       </c>
-      <c r="E14" s="157" t="n"/>
+      <c r="E14" s="192" t="n"/>
       <c r="F14" s="82" t="n"/>
       <c r="G14" s="83" t="n"/>
       <c r="H14" s="79" t="n"/>
@@ -3930,7 +5507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF99CCFF"/>
@@ -3949,7 +5526,7 @@
     <col width="17.6640625" customWidth="1" style="39" min="7" max="7"/>
     <col width="15.6640625" customWidth="1" style="39" min="8" max="8"/>
     <col width="14.88671875" customWidth="1" style="39" min="9" max="9"/>
-    <col width="30.33203125" customWidth="1" style="133" min="10" max="10"/>
+    <col width="30.33203125" customWidth="1" style="168" min="10" max="10"/>
     <col width="3.109375" customWidth="1" style="39" min="11" max="11"/>
     <col width="8.88671875" customWidth="1" style="39" min="12" max="16384"/>
   </cols>
@@ -3963,124 +5540,124 @@
       </c>
     </row>
     <row r="2" ht="41.25" customHeight="1" thickBot="1">
-      <c r="B2" s="154" t="inlineStr">
+      <c r="B2" s="191" t="inlineStr">
         <is>
           <t>PFMEA - Occurrence
 The team should agree on the criteria and ranking values. Select one way and consistently apply that scale.</t>
         </is>
       </c>
-      <c r="C2" s="155" t="n"/>
-      <c r="D2" s="155" t="n"/>
-      <c r="E2" s="155" t="n"/>
-      <c r="F2" s="155" t="n"/>
-      <c r="G2" s="155" t="n"/>
-      <c r="H2" s="155" t="n"/>
-      <c r="I2" s="155" t="n"/>
-      <c r="J2" s="156" t="n"/>
+      <c r="C2" s="178" t="n"/>
+      <c r="D2" s="178" t="n"/>
+      <c r="E2" s="178" t="n"/>
+      <c r="F2" s="178" t="n"/>
+      <c r="G2" s="178" t="n"/>
+      <c r="H2" s="178" t="n"/>
+      <c r="I2" s="178" t="n"/>
+      <c r="J2" s="179" t="n"/>
     </row>
     <row r="3" ht="26.25" customHeight="1" thickBot="1">
-      <c r="B3" s="134" t="inlineStr">
+      <c r="B3" s="169" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="C3" s="134" t="inlineStr">
+      <c r="C3" s="169" t="inlineStr">
         <is>
           <t>J1739</t>
         </is>
       </c>
-      <c r="D3" s="134" t="inlineStr">
+      <c r="D3" s="169" t="inlineStr">
         <is>
           <t>AS13004</t>
         </is>
       </c>
-      <c r="E3" s="155" t="n"/>
-      <c r="F3" s="155" t="n"/>
-      <c r="G3" s="156" t="n"/>
-      <c r="H3" s="134" t="inlineStr">
+      <c r="E3" s="178" t="n"/>
+      <c r="F3" s="178" t="n"/>
+      <c r="G3" s="179" t="n"/>
+      <c r="H3" s="169" t="inlineStr">
         <is>
           <t>AIAG FMEA - 4th Edition</t>
         </is>
       </c>
-      <c r="I3" s="134" t="inlineStr">
+      <c r="I3" s="169" t="inlineStr">
         <is>
           <t>J1739</t>
         </is>
       </c>
-      <c r="J3" s="124" t="inlineStr">
+      <c r="J3" s="159" t="inlineStr">
         <is>
           <t>Examples</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="124" t="inlineStr">
+      <c r="B4" s="159" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="C4" s="124" t="inlineStr">
+      <c r="C4" s="159" t="inlineStr">
         <is>
           <t>Likelihood of
 Failure</t>
         </is>
       </c>
-      <c r="D4" s="124" t="inlineStr">
+      <c r="D4" s="159" t="inlineStr">
         <is>
           <t>Low volume production</t>
         </is>
       </c>
-      <c r="E4" s="156" t="n"/>
-      <c r="F4" s="124" t="inlineStr">
+      <c r="E4" s="179" t="n"/>
+      <c r="F4" s="159" t="inlineStr">
         <is>
           <t>Process PPM</t>
         </is>
       </c>
-      <c r="G4" s="124" t="inlineStr">
+      <c r="G4" s="159" t="inlineStr">
         <is>
           <t>Time-Based Example</t>
         </is>
       </c>
-      <c r="H4" s="124" t="inlineStr">
+      <c r="H4" s="159" t="inlineStr">
         <is>
           <t>High volume production</t>
         </is>
       </c>
-      <c r="I4" s="156" t="n"/>
-      <c r="J4" s="159" t="n"/>
+      <c r="I4" s="179" t="n"/>
+      <c r="J4" s="194" t="n"/>
     </row>
     <row r="5" ht="29.4" customHeight="1" thickBot="1">
-      <c r="B5" s="157" t="n"/>
-      <c r="C5" s="157" t="n"/>
-      <c r="D5" s="124" t="inlineStr">
+      <c r="B5" s="192" t="n"/>
+      <c r="C5" s="192" t="n"/>
+      <c r="D5" s="159" t="inlineStr">
         <is>
           <t>Likelihood of Cause</t>
         </is>
       </c>
-      <c r="E5" s="124" t="inlineStr">
+      <c r="E5" s="159" t="inlineStr">
         <is>
           <t>Time-Based Example</t>
         </is>
       </c>
-      <c r="F5" s="157" t="n"/>
-      <c r="G5" s="157" t="n"/>
-      <c r="H5" s="124" t="inlineStr">
+      <c r="F5" s="192" t="n"/>
+      <c r="G5" s="192" t="n"/>
+      <c r="H5" s="159" t="inlineStr">
         <is>
           <t>Likelihood of Cause</t>
         </is>
       </c>
-      <c r="I5" s="124" t="inlineStr">
+      <c r="I5" s="159" t="inlineStr">
         <is>
           <t>Incidents per item/unit</t>
         </is>
       </c>
-      <c r="J5" s="157" t="n"/>
+      <c r="J5" s="192" t="n"/>
     </row>
     <row r="6" ht="41.25" customHeight="1" thickBot="1">
       <c r="B6" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="166" t="inlineStr">
         <is>
           <t>Very High</t>
         </is>
@@ -4090,7 +5667,7 @@
           <t>100% of production</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per occurrence per shift</t>
         </is>
@@ -4098,7 +5675,7 @@
       <c r="F6" s="62" t="n">
         <v>500000</v>
       </c>
-      <c r="G6" s="131" t="inlineStr">
+      <c r="G6" s="166" t="inlineStr">
         <is>
           <t>&gt; 1 per occurrence per shift</t>
         </is>
@@ -4108,7 +5685,7 @@
           <t>1 in 10</t>
         </is>
       </c>
-      <c r="I6" s="131" t="inlineStr">
+      <c r="I6" s="166" t="inlineStr">
         <is>
           <t>&gt; 100 per thousand</t>
         </is>
@@ -4119,7 +5696,7 @@
       <c r="B7" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="166" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4129,7 +5706,7 @@
           <t>50% of production</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per occurrence per day</t>
         </is>
@@ -4137,12 +5714,12 @@
       <c r="F7" s="62" t="n">
         <v>50000</v>
       </c>
-      <c r="G7" s="131" t="inlineStr">
+      <c r="G7" s="166" t="inlineStr">
         <is>
           <t>&gt; 1 per occurrence per day</t>
         </is>
       </c>
-      <c r="H7" s="131" t="inlineStr">
+      <c r="H7" s="166" t="inlineStr">
         <is>
           <t>1 in 20</t>
         </is>
@@ -4158,13 +5735,13 @@
       <c r="B8" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="159" t="n"/>
+      <c r="C8" s="194" t="n"/>
       <c r="D8" s="61" t="inlineStr">
         <is>
           <t>20% of production</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per 2-3 days</t>
         </is>
@@ -4172,12 +5749,12 @@
       <c r="F8" s="62" t="n">
         <v>20000</v>
       </c>
-      <c r="G8" s="131" t="inlineStr">
+      <c r="G8" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per 2-3 days</t>
         </is>
       </c>
-      <c r="H8" s="131" t="inlineStr">
+      <c r="H8" s="166" t="inlineStr">
         <is>
           <t>1 in 50</t>
         </is>
@@ -4193,13 +5770,13 @@
       <c r="B9" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="157" t="n"/>
+      <c r="C9" s="192" t="n"/>
       <c r="D9" s="61" t="inlineStr">
         <is>
           <t>10% of production</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per week</t>
         </is>
@@ -4207,12 +5784,12 @@
       <c r="F9" s="62" t="n">
         <v>10000</v>
       </c>
-      <c r="G9" s="131" t="inlineStr">
+      <c r="G9" s="166" t="inlineStr">
         <is>
           <t>&gt; 1 per week</t>
         </is>
       </c>
-      <c r="H9" s="131" t="inlineStr">
+      <c r="H9" s="166" t="inlineStr">
         <is>
           <t>1 in 100</t>
         </is>
@@ -4228,7 +5805,7 @@
       <c r="B10" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="166" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4238,7 +5815,7 @@
           <t>5% of production</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="166" t="inlineStr">
         <is>
           <t>1 per month</t>
         </is>
@@ -4246,12 +5823,12 @@
       <c r="F10" s="62" t="n">
         <v>5000</v>
       </c>
-      <c r="G10" s="131" t="inlineStr">
+      <c r="G10" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per 2 weeks</t>
         </is>
       </c>
-      <c r="H10" s="131" t="inlineStr">
+      <c r="H10" s="166" t="inlineStr">
         <is>
           <t>1 in 500</t>
         </is>
@@ -4267,13 +5844,13 @@
       <c r="B11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="159" t="n"/>
+      <c r="C11" s="194" t="n"/>
       <c r="D11" s="61" t="inlineStr">
         <is>
           <t>0.5% of production</t>
         </is>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="166" t="inlineStr">
         <is>
           <t>2 per year</t>
         </is>
@@ -4281,12 +5858,12 @@
       <c r="F11" s="62" t="n">
         <v>1000</v>
       </c>
-      <c r="G11" s="131" t="inlineStr">
+      <c r="G11" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per quarter</t>
         </is>
       </c>
-      <c r="H11" s="131" t="inlineStr">
+      <c r="H11" s="166" t="inlineStr">
         <is>
           <t>1 in 2,000</t>
         </is>
@@ -4302,26 +5879,26 @@
       <c r="B12" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="157" t="n"/>
+      <c r="C12" s="192" t="n"/>
       <c r="D12" s="61" t="inlineStr">
         <is>
           <t>0.1% of production</t>
         </is>
       </c>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="166" t="inlineStr">
         <is>
           <t>1 per year</t>
         </is>
       </c>
-      <c r="F12" s="131" t="n">
+      <c r="F12" s="166" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="131" t="inlineStr">
+      <c r="G12" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per half year</t>
         </is>
       </c>
-      <c r="H12" s="131" t="inlineStr">
+      <c r="H12" s="166" t="inlineStr">
         <is>
           <t>1 in 10,000</t>
         </is>
@@ -4337,7 +5914,7 @@
       <c r="B13" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="166" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4347,20 +5924,20 @@
           <t>0.05% of production</t>
         </is>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="166" t="inlineStr">
         <is>
           <t>1 per 5 years</t>
         </is>
       </c>
-      <c r="F13" s="131" t="n">
+      <c r="F13" s="166" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="131" t="inlineStr">
+      <c r="G13" s="166" t="inlineStr">
         <is>
           <t>&gt;1 per year</t>
         </is>
       </c>
-      <c r="H13" s="131" t="inlineStr">
+      <c r="H13" s="166" t="inlineStr">
         <is>
           <t>1 in 100,000</t>
         </is>
@@ -4376,26 +5953,26 @@
       <c r="B14" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="157" t="n"/>
+      <c r="C14" s="192" t="n"/>
       <c r="D14" s="61" t="inlineStr">
         <is>
           <t>0.01% of production</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="166" t="inlineStr">
         <is>
           <t>1 per 10 years</t>
         </is>
       </c>
-      <c r="F14" s="131" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="131" t="inlineStr">
+      <c r="F14" s="166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="166" t="inlineStr">
         <is>
           <t>&lt;1 per year</t>
         </is>
       </c>
-      <c r="H14" s="131" t="inlineStr">
+      <c r="H14" s="166" t="inlineStr">
         <is>
           <t>1 in 1,000,000</t>
         </is>
@@ -4411,7 +5988,7 @@
       <c r="B15" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="166" t="inlineStr">
         <is>
           <t>Very Low</t>
         </is>
@@ -4421,17 +5998,17 @@
           <t>Less than 0.01% of production</t>
         </is>
       </c>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="166" t="inlineStr">
         <is>
           <t>&lt;1 per 10 years</t>
         </is>
       </c>
-      <c r="F15" s="131" t="inlineStr">
+      <c r="F15" s="166" t="inlineStr">
         <is>
           <t>zero</t>
         </is>
       </c>
-      <c r="G15" s="131" t="inlineStr">
+      <c r="G15" s="166" t="inlineStr">
         <is>
           <t>Never</t>
         </is>
@@ -4468,7 +6045,7 @@
       </c>
     </row>
     <row r="17" hidden="1">
-      <c r="B17" s="132" t="n"/>
+      <c r="B17" s="167" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="70" t="n"/>
@@ -4484,8 +6061,8 @@
       <c r="B20" s="71" t="n"/>
       <c r="C20" s="71" t="n"/>
       <c r="D20" s="72" t="n"/>
-      <c r="H20" s="133" t="n"/>
-      <c r="I20" s="133" t="n"/>
+      <c r="H20" s="168" t="n"/>
+      <c r="I20" s="168" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="71" t="n"/>
@@ -4531,7 +6108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF99CCFF"/>
@@ -4561,73 +6138,73 @@
       </c>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
-      <c r="B2" s="154" t="inlineStr">
+      <c r="B2" s="191" t="inlineStr">
         <is>
           <t>PFMEA - Severity
 The team should agree on the criteria and ranking values. Select one way and consistently apply that scale.</t>
         </is>
       </c>
-      <c r="C2" s="155" t="n"/>
-      <c r="D2" s="155" t="n"/>
-      <c r="E2" s="155" t="n"/>
-      <c r="F2" s="155" t="n"/>
-      <c r="G2" s="156" t="n"/>
+      <c r="C2" s="178" t="n"/>
+      <c r="D2" s="178" t="n"/>
+      <c r="E2" s="178" t="n"/>
+      <c r="F2" s="178" t="n"/>
+      <c r="G2" s="179" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1" thickBot="1">
-      <c r="B3" s="134" t="inlineStr">
+      <c r="B3" s="169" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="C3" s="134" t="inlineStr">
+      <c r="C3" s="169" t="inlineStr">
         <is>
           <t>Modified from J1739 / AS13004</t>
         </is>
       </c>
-      <c r="D3" s="155" t="n"/>
-      <c r="E3" s="155" t="n"/>
-      <c r="F3" s="156" t="n"/>
-      <c r="G3" s="124" t="inlineStr">
+      <c r="D3" s="178" t="n"/>
+      <c r="E3" s="178" t="n"/>
+      <c r="F3" s="179" t="n"/>
+      <c r="G3" s="159" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29.4" customHeight="1" thickBot="1">
-      <c r="B4" s="124" t="inlineStr">
+      <c r="B4" s="159" t="inlineStr">
         <is>
           <t>Effect</t>
         </is>
       </c>
-      <c r="C4" s="124" t="inlineStr">
+      <c r="C4" s="159" t="inlineStr">
         <is>
           <t>Severity of Effect on Product (Customer Effect)</t>
         </is>
       </c>
-      <c r="D4" s="124" t="inlineStr">
+      <c r="D4" s="159" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
-      <c r="E4" s="124" t="inlineStr">
+      <c r="E4" s="159" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F4" s="124" t="inlineStr">
+      <c r="F4" s="159" t="inlineStr">
         <is>
           <t>Severity of Effect on Process (Manufacturing / Assembly Effect)</t>
         </is>
       </c>
-      <c r="G4" s="157" t="n"/>
+      <c r="G4" s="192" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1" thickBot="1">
-      <c r="B5" s="131" t="inlineStr">
+      <c r="B5" s="166" t="inlineStr">
         <is>
           <t>Failure to meet safety and/or regulatory requirements</t>
         </is>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="166" t="inlineStr">
         <is>
           <t>Potential failure mode affects safe operation and/or involves noncompliance with regulations without warning</t>
         </is>
@@ -4635,12 +6212,12 @@
       <c r="D5" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="166" t="inlineStr">
         <is>
           <t>Failure to meet safety and/or regulatory requirements</t>
         </is>
       </c>
-      <c r="F5" s="131" t="inlineStr">
+      <c r="F5" s="166" t="inlineStr">
         <is>
           <t>May endanger operator, machine or assembly without warning.</t>
         </is>
@@ -4648,8 +6225,8 @@
       <c r="G5" s="46" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1" thickBot="1">
-      <c r="B6" s="157" t="n"/>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="B6" s="192" t="n"/>
+      <c r="C6" s="166" t="inlineStr">
         <is>
           <t>Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning</t>
         </is>
@@ -4657,8 +6234,8 @@
       <c r="D6" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="157" t="n"/>
-      <c r="F6" s="131" t="inlineStr">
+      <c r="E6" s="192" t="n"/>
+      <c r="F6" s="166" t="inlineStr">
         <is>
           <t>May endanger operator, machine or assembly with warning.</t>
         </is>
@@ -4666,12 +6243,12 @@
       <c r="G6" s="46" t="n"/>
     </row>
     <row r="7" ht="57.6" customHeight="1" thickBot="1">
-      <c r="B7" s="131" t="inlineStr">
+      <c r="B7" s="166" t="inlineStr">
         <is>
           <t>Loss or degradation of primary function</t>
         </is>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="166" t="inlineStr">
         <is>
           <t>Loss of primary function (product inoperable, does not affect safe operation)</t>
         </is>
@@ -4679,12 +6256,12 @@
       <c r="D7" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="166" t="inlineStr">
         <is>
           <t>Major disruption</t>
         </is>
       </c>
-      <c r="F7" s="131" t="inlineStr">
+      <c r="F7" s="166" t="inlineStr">
         <is>
           <t>100% of product may have to be scrapped. Line shutdown or stop ship.</t>
         </is>
@@ -4692,8 +6269,8 @@
       <c r="G7" s="46" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1" thickBot="1">
-      <c r="B8" s="157" t="n"/>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="B8" s="192" t="n"/>
+      <c r="C8" s="166" t="inlineStr">
         <is>
           <t>Degradation of primary function (product operable, but at a reduced level of performance)</t>
         </is>
@@ -4701,12 +6278,12 @@
       <c r="D8" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="166" t="inlineStr">
         <is>
           <t>Significant disruption</t>
         </is>
       </c>
-      <c r="F8" s="131" t="inlineStr">
+      <c r="F8" s="166" t="inlineStr">
         <is>
           <t>A portion of the production run may have to be scrapped. Deviation from primary process; decreased line speed or added manpower).</t>
         </is>
@@ -4714,12 +6291,12 @@
       <c r="G8" s="46" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1" thickBot="1">
-      <c r="B9" s="131" t="inlineStr">
+      <c r="B9" s="166" t="inlineStr">
         <is>
           <t>Loss or degradation of secondary function</t>
         </is>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="166" t="inlineStr">
         <is>
           <t xml:space="preserve">Loss of secondary function (product operable but service life greatly reduced, convenience item(s) inoperable, customer dissatisfied) </t>
         </is>
@@ -4727,12 +6304,12 @@
       <c r="D9" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="166" t="inlineStr">
         <is>
           <t>Moderate disruption</t>
         </is>
       </c>
-      <c r="F9" s="131" t="inlineStr">
+      <c r="F9" s="166" t="inlineStr">
         <is>
           <t>100% of production run may have to be reworked off line and accepted</t>
         </is>
@@ -4740,8 +6317,8 @@
       <c r="G9" s="46" t="n"/>
     </row>
     <row r="10" ht="55.8" customHeight="1" thickBot="1">
-      <c r="B10" s="157" t="n"/>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="B10" s="192" t="n"/>
+      <c r="C10" s="166" t="inlineStr">
         <is>
           <t>Degradation of secondary function (product operable but appearance affected, convenience item(s)  operable at a reduced level, customer dissatisfied.</t>
         </is>
@@ -4749,8 +6326,8 @@
       <c r="D10" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="157" t="n"/>
-      <c r="F10" s="131" t="inlineStr">
+      <c r="E10" s="192" t="n"/>
+      <c r="F10" s="166" t="inlineStr">
         <is>
           <t xml:space="preserve">A proportion of the production run may have to be reworked off line and acepted </t>
         </is>
@@ -4758,12 +6335,12 @@
       <c r="G10" s="46" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1" thickBot="1">
-      <c r="B11" s="131" t="inlineStr">
+      <c r="B11" s="166" t="inlineStr">
         <is>
           <t>Annoyance</t>
         </is>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="166" t="inlineStr">
         <is>
           <t>Appearance, fit and finish type items do not conform, defect noticed by most of the customers (&gt;75%)</t>
         </is>
@@ -4771,12 +6348,12 @@
       <c r="D11" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="166" t="inlineStr">
         <is>
           <t>Moderate disruption</t>
         </is>
       </c>
-      <c r="F11" s="131" t="inlineStr">
+      <c r="F11" s="166" t="inlineStr">
         <is>
           <t>100% of production run may have to be reworked in station before it is processed.</t>
         </is>
@@ -4784,8 +6361,8 @@
       <c r="G11" s="46" t="n"/>
     </row>
     <row r="12" ht="42" customHeight="1" thickBot="1">
-      <c r="B12" s="159" t="n"/>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="B12" s="194" t="n"/>
+      <c r="C12" s="166" t="inlineStr">
         <is>
           <t>Appearance, fit and finish type items do not conform, defect noticed by about half of the customers (50%)</t>
         </is>
@@ -4793,8 +6370,8 @@
       <c r="D12" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="157" t="n"/>
-      <c r="F12" s="131" t="inlineStr">
+      <c r="E12" s="192" t="n"/>
+      <c r="F12" s="166" t="inlineStr">
         <is>
           <t>A proportion of the production run may have to be reworked in station before it is processed.</t>
         </is>
@@ -4802,8 +6379,8 @@
       <c r="G12" s="46" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1" thickBot="1">
-      <c r="B13" s="157" t="n"/>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="B13" s="192" t="n"/>
+      <c r="C13" s="166" t="inlineStr">
         <is>
           <t>Appearance, fit and finish type items do not conform, defect noticed by discriminating customers (&lt;25%)</t>
         </is>
@@ -4811,12 +6388,12 @@
       <c r="D13" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="166" t="inlineStr">
         <is>
           <t>Minor disruption</t>
         </is>
       </c>
-      <c r="F13" s="131" t="inlineStr">
+      <c r="F13" s="166" t="inlineStr">
         <is>
           <t>Slight inconvenience to process, operation or operator.</t>
         </is>
@@ -4824,12 +6401,12 @@
       <c r="G13" s="46" t="n"/>
     </row>
     <row r="14" ht="18.6" customHeight="1" thickBot="1">
-      <c r="B14" s="131" t="inlineStr">
+      <c r="B14" s="166" t="inlineStr">
         <is>
           <t>No effect</t>
         </is>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="166" t="inlineStr">
         <is>
           <t>No discernible effect</t>
         </is>
@@ -4837,12 +6414,12 @@
       <c r="D14" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="166" t="inlineStr">
         <is>
           <t>No effect</t>
         </is>
       </c>
-      <c r="F14" s="131" t="inlineStr">
+      <c r="F14" s="166" t="inlineStr">
         <is>
           <t>No discernible effect</t>
         </is>
@@ -4892,7 +6469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4923,44 +6500,44 @@
       <c r="B2" s="9" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="160" t="inlineStr">
+      <c r="A3" s="195" t="inlineStr">
         <is>
           <t>1.  All provisions of Product Resources' ISO 9001 QMS apply and are implemented.</t>
         </is>
       </c>
-      <c r="B3" s="161" t="n"/>
+      <c r="B3" s="196" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="160" t="inlineStr">
+      <c r="A4" s="195" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B4" s="161" t="n"/>
+      <c r="B4" s="196" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="160" t="inlineStr">
+      <c r="A5" s="195" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B5" s="161" t="n"/>
+      <c r="B5" s="196" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="160" t="inlineStr">
+      <c r="A6" s="195" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B6" s="161" t="n"/>
+      <c r="B6" s="196" t="n"/>
     </row>
     <row r="7" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A7" s="162" t="inlineStr">
+      <c r="A7" s="197" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B7" s="163" t="n"/>
+      <c r="B7" s="198" t="n"/>
     </row>
     <row r="8" ht="14.4" customHeight="1" thickBot="1" thickTop="1">
       <c r="A8" s="5" t="n"/>
@@ -5335,4 +6912,1476 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="16.6640625" customWidth="1" min="1" max="1"/>
+    <col width="25.6640625" customWidth="1" min="2" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="3.109375" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="3.109375" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="7"/>
+    <col width="3.6640625" customWidth="1" min="7" max="7"/>
+    <col width="28.5546875" customWidth="1" style="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="5.44140625" customWidth="1" min="10" max="10"/>
+    <col width="23.33203125" customWidth="1" style="1" min="11" max="11"/>
+    <col width="5.109375" customWidth="1" min="12" max="12"/>
+    <col width="5.109375" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="5.6640625" customWidth="1" min="15" max="15"/>
+    <col width="16.6640625" customWidth="1" min="16" max="16"/>
+    <col width="5.6640625" customWidth="1" style="1" min="17" max="17"/>
+    <col width="19.6640625" bestFit="1" customWidth="1" style="1" min="18" max="20"/>
+    <col width="11.77734375" customWidth="1" min="19" max="19"/>
+    <col width="11.77734375" customWidth="1" min="20" max="20"/>
+    <col width="13.44140625" customWidth="1" style="1" min="21" max="21"/>
+    <col width="13.44140625" customWidth="1" min="22" max="22"/>
+    <col width="13.109375" customWidth="1" min="23" max="23"/>
+    <col width="13.109375" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30.6" customHeight="1">
+      <c r="A1" s="113" t="inlineStr">
+        <is>
+          <t>Quality Tools</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="19" t="n"/>
+      <c r="D1" s="18" t="n"/>
+      <c r="E1" s="18" t="n"/>
+      <c r="F1" s="34" t="inlineStr">
+        <is>
+          <t>Process FMEA</t>
+        </is>
+      </c>
+      <c r="G1" s="34" t="n"/>
+      <c r="H1" s="18" t="n"/>
+      <c r="I1" s="19" t="n"/>
+      <c r="J1" s="19" t="n"/>
+      <c r="K1" s="18" t="n"/>
+      <c r="L1" s="19" t="n"/>
+      <c r="M1" s="19" t="n"/>
+      <c r="N1" s="19" t="n"/>
+      <c r="O1" s="19" t="n"/>
+      <c r="P1" s="19" t="n"/>
+      <c r="Q1" s="18" t="n"/>
+      <c r="R1" s="18" t="n"/>
+      <c r="S1" s="18" t="n"/>
+      <c r="T1" s="18" t="n"/>
+      <c r="U1" s="18" t="n"/>
+    </row>
+    <row r="2" ht="16.2" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Failure Mode and Effects Analysis</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" s="19" t="n"/>
+      <c r="Q2" s="18" t="n"/>
+      <c r="R2" s="18" t="n"/>
+      <c r="S2" s="18" t="n"/>
+      <c r="T2" s="18" t="n"/>
+      <c r="U2" s="18" t="n"/>
+    </row>
+    <row r="3" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Instructions</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="19" t="n"/>
+      <c r="M3" s="19" t="n"/>
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="19" t="n"/>
+      <c r="P3" s="19" t="n"/>
+      <c r="Q3" s="18" t="n"/>
+      <c r="R3" s="18" t="n"/>
+      <c r="S3" s="18" t="n"/>
+      <c r="T3" s="18" t="n"/>
+      <c r="U3" s="18" t="n"/>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This template is for use by Product Resources to record the Process Failure Mode and Effects Analysis (DFMEA) for medical and other devices.  FMEA is also referred to as Failure Modes, Effects, and Criticality Analysis (FMECA).  </t>
+        </is>
+      </c>
+      <c r="B4" s="184" t="n"/>
+      <c r="C4" s="184" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F4" s="114" t="inlineStr">
+        <is>
+          <t>Please see the guidance in 90-2000-7.1 regarding FMEA process before beginning an FMEA</t>
+        </is>
+      </c>
+      <c r="G4" s="184" t="n"/>
+      <c r="H4" s="184" t="n"/>
+      <c r="I4" s="124" t="n"/>
+      <c r="J4" s="24" t="n"/>
+      <c r="K4" s="18" t="n"/>
+      <c r="L4" s="112" t="inlineStr">
+        <is>
+          <t>Parameters:</t>
+        </is>
+      </c>
+      <c r="M4" s="185" t="n"/>
+      <c r="N4" s="185" t="n"/>
+      <c r="O4" s="185" t="n"/>
+      <c r="P4" s="185" t="n"/>
+      <c r="Q4" s="185" t="n"/>
+      <c r="R4" s="185" t="n"/>
+      <c r="S4" s="186" t="n"/>
+      <c r="T4" s="112" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="U4" s="186" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n"/>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F5" s="124" t="inlineStr">
+        <is>
+          <t>Initiate action to reduce the RPN</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="124" t="n"/>
+      <c r="J5" s="24" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="112" t="inlineStr">
+        <is>
+          <t>RPN triggering requiring mitigation action:</t>
+        </is>
+      </c>
+      <c r="M5" s="185" t="n"/>
+      <c r="N5" s="185" t="n"/>
+      <c r="O5" s="185" t="n"/>
+      <c r="P5" s="185" t="n"/>
+      <c r="Q5" s="185" t="n"/>
+      <c r="R5" s="185" t="n"/>
+      <c r="S5" s="185" t="n"/>
+      <c r="T5" s="186" t="n"/>
+      <c r="U5" s="26" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="19" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="F6" s="124" t="inlineStr">
+        <is>
+          <t>Re-evaluate the RPN value after completion of the recommended actions</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="124" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="112" t="inlineStr">
+        <is>
+          <t>Severity (Sev) requiring mitigation action regardless of RPN:</t>
+        </is>
+      </c>
+      <c r="M6" s="185" t="n"/>
+      <c r="N6" s="185" t="n"/>
+      <c r="O6" s="185" t="n"/>
+      <c r="P6" s="185" t="n"/>
+      <c r="Q6" s="185" t="n"/>
+      <c r="R6" s="185" t="n"/>
+      <c r="S6" s="185" t="n"/>
+      <c r="T6" s="186" t="n"/>
+      <c r="U6" s="26" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" customHeight="1">
+      <c r="A7" s="111" t="inlineStr">
+        <is>
+          <t>PROCESS FAILURE MODE AND EFFECTS ANALYSIS (PFMEA)</t>
+        </is>
+      </c>
+      <c r="B7" s="185" t="n"/>
+      <c r="C7" s="185" t="n"/>
+      <c r="D7" s="185" t="n"/>
+      <c r="E7" s="185" t="n"/>
+      <c r="F7" s="185" t="n"/>
+      <c r="G7" s="185" t="n"/>
+      <c r="H7" s="185" t="n"/>
+      <c r="I7" s="185" t="n"/>
+      <c r="J7" s="185" t="n"/>
+      <c r="K7" s="185" t="n"/>
+      <c r="L7" s="185" t="n"/>
+      <c r="M7" s="185" t="n"/>
+      <c r="N7" s="185" t="n"/>
+      <c r="O7" s="185" t="n"/>
+      <c r="P7" s="185" t="n"/>
+      <c r="Q7" s="185" t="n"/>
+      <c r="R7" s="185" t="n"/>
+      <c r="S7" s="185" t="n"/>
+      <c r="T7" s="185" t="n"/>
+      <c r="U7" s="186" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Item:</t>
+        </is>
+      </c>
+      <c r="B8" s="120" t="inlineStr">
+        <is>
+          <t>Wheel damper</t>
+        </is>
+      </c>
+      <c r="C8" s="185" t="n"/>
+      <c r="D8" s="186" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="130" t="inlineStr">
+        <is>
+          <t>Responsibility:</t>
+        </is>
+      </c>
+      <c r="G8" s="185" t="n"/>
+      <c r="H8" s="186" t="n"/>
+      <c r="I8" s="120" t="inlineStr">
+        <is>
+          <t>Donald Trump</t>
+        </is>
+      </c>
+      <c r="J8" s="185" t="n"/>
+      <c r="K8" s="186" t="n"/>
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="28" t="n"/>
+      <c r="N8" s="28" t="n"/>
+      <c r="O8" s="28" t="n"/>
+      <c r="P8" s="27" t="inlineStr">
+        <is>
+          <t>FMEA number:</t>
+        </is>
+      </c>
+      <c r="Q8" s="120" t="inlineStr">
+        <is>
+          <t>Filename</t>
+        </is>
+      </c>
+      <c r="R8" s="185" t="n"/>
+      <c r="S8" s="185" t="n"/>
+      <c r="T8" s="185" t="n"/>
+      <c r="U8" s="186" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B9" s="120" t="inlineStr">
+        <is>
+          <t>Drive shaft</t>
+        </is>
+      </c>
+      <c r="C9" s="185" t="n"/>
+      <c r="D9" s="186" t="n"/>
+      <c r="E9" s="129" t="n"/>
+      <c r="F9" s="121" t="inlineStr">
+        <is>
+          <t>Prepared by:</t>
+        </is>
+      </c>
+      <c r="G9" s="185" t="n"/>
+      <c r="H9" s="186" t="n"/>
+      <c r="I9" s="120" t="inlineStr">
+        <is>
+          <t>Selva Jeyaseelan</t>
+        </is>
+      </c>
+      <c r="J9" s="185" t="n"/>
+      <c r="K9" s="186" t="n"/>
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="28" t="n"/>
+      <c r="N9" s="28" t="n"/>
+      <c r="O9" s="28" t="n"/>
+      <c r="P9" s="27" t="inlineStr">
+        <is>
+          <t>Page :</t>
+        </is>
+      </c>
+      <c r="Q9" s="129" t="n"/>
+      <c r="R9" s="185" t="n"/>
+      <c r="S9" s="185" t="n"/>
+      <c r="T9" s="185" t="n"/>
+      <c r="U9" s="186" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Core Team:</t>
+        </is>
+      </c>
+      <c r="B10" s="125" t="inlineStr">
+        <is>
+          <t>Sunder Pichai, Sam Altman, Selva Jeyaseelan</t>
+        </is>
+      </c>
+      <c r="C10" s="185" t="n"/>
+      <c r="D10" s="185" t="n"/>
+      <c r="E10" s="185" t="n"/>
+      <c r="F10" s="185" t="n"/>
+      <c r="G10" s="185" t="n"/>
+      <c r="H10" s="185" t="n"/>
+      <c r="I10" s="185" t="n"/>
+      <c r="J10" s="185" t="n"/>
+      <c r="K10" s="186" t="n"/>
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="28" t="n"/>
+      <c r="N10" s="28" t="n"/>
+      <c r="O10" s="28" t="n"/>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>FMEA Date (Orig):</t>
+        </is>
+      </c>
+      <c r="Q10" s="30" t="n">
+        <v>46270</v>
+      </c>
+      <c r="R10" s="131" t="inlineStr">
+        <is>
+          <t>Rev:</t>
+        </is>
+      </c>
+      <c r="S10" s="186" t="n"/>
+      <c r="T10" s="132" t="n"/>
+      <c r="U10" s="186" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="31" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="28" t="n"/>
+      <c r="N11" s="28" t="n"/>
+      <c r="O11" s="28" t="n"/>
+      <c r="P11" s="27" t="inlineStr">
+        <is>
+          <t>FMEA Date (Cur):</t>
+        </is>
+      </c>
+      <c r="Q11" s="30" t="n">
+        <v>46270</v>
+      </c>
+      <c r="R11" s="131" t="inlineStr">
+        <is>
+          <t>Rev:</t>
+        </is>
+      </c>
+      <c r="S11" s="186" t="n"/>
+      <c r="T11" s="132" t="n"/>
+      <c r="U11" s="186" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="187" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="B12" s="107" t="inlineStr">
+        <is>
+          <t>Potential Failure Mode</t>
+        </is>
+      </c>
+      <c r="C12" s="107" t="inlineStr">
+        <is>
+          <t>Potential Effects of Failure</t>
+        </is>
+      </c>
+      <c r="D12" s="107" t="inlineStr">
+        <is>
+          <t>Sev</t>
+        </is>
+      </c>
+      <c r="E12" s="107" t="inlineStr">
+        <is>
+          <t>Pred Sev</t>
+        </is>
+      </c>
+      <c r="F12" s="107" t="inlineStr">
+        <is>
+          <t>Sev Reasoning</t>
+        </is>
+      </c>
+      <c r="G12" s="107" t="inlineStr">
+        <is>
+          <t>Cls</t>
+        </is>
+      </c>
+      <c r="H12" s="107" t="inlineStr">
+        <is>
+          <t>Potential Causes / Mechanisms of Failure</t>
+        </is>
+      </c>
+      <c r="I12" s="107" t="inlineStr">
+        <is>
+          <t>Current Process Prevention Controls</t>
+        </is>
+      </c>
+      <c r="J12" s="107" t="inlineStr">
+        <is>
+          <t>Occ</t>
+        </is>
+      </c>
+      <c r="K12" s="107" t="inlineStr">
+        <is>
+          <t>Current Process Detection Controls</t>
+        </is>
+      </c>
+      <c r="L12" s="107" t="inlineStr">
+        <is>
+          <t>Det</t>
+        </is>
+      </c>
+      <c r="M12" s="107" t="inlineStr">
+        <is>
+          <t>Pred Det</t>
+        </is>
+      </c>
+      <c r="N12" s="107" t="inlineStr">
+        <is>
+          <t>Det Reasoning</t>
+        </is>
+      </c>
+      <c r="O12" s="107" t="inlineStr">
+        <is>
+          <t>RPN</t>
+        </is>
+      </c>
+      <c r="P12" s="107" t="inlineStr">
+        <is>
+          <t>D-P gap</t>
+        </is>
+      </c>
+      <c r="Q12" s="107" t="inlineStr">
+        <is>
+          <t>New RPN</t>
+        </is>
+      </c>
+      <c r="R12" s="107" t="inlineStr">
+        <is>
+          <t>Recommended Actions</t>
+        </is>
+      </c>
+      <c r="S12" s="107" t="inlineStr">
+        <is>
+          <t>Severity Zone</t>
+        </is>
+      </c>
+      <c r="T12" s="107" t="inlineStr">
+        <is>
+          <t>Pred Sev Zone</t>
+        </is>
+      </c>
+      <c r="U12" s="107" t="inlineStr">
+        <is>
+          <t>Detection Zone</t>
+        </is>
+      </c>
+      <c r="V12" s="107" t="inlineStr">
+        <is>
+          <t>Pred Det Zone</t>
+        </is>
+      </c>
+      <c r="W12" s="107" t="inlineStr">
+        <is>
+          <t>Priority Level</t>
+        </is>
+      </c>
+      <c r="X12" s="107" t="inlineStr">
+        <is>
+          <t>Pred Priority Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="188" t="n"/>
+      <c r="B13" s="188" t="n"/>
+      <c r="C13" s="188" t="n"/>
+      <c r="D13" s="188" t="n"/>
+      <c r="E13" s="188" t="n"/>
+      <c r="F13" s="188" t="n"/>
+      <c r="G13" s="188" t="n"/>
+      <c r="H13" s="188" t="n"/>
+      <c r="I13" s="188" t="n"/>
+      <c r="J13" s="188" t="n"/>
+      <c r="K13" s="188" t="n"/>
+      <c r="L13" s="188" t="n"/>
+      <c r="M13" s="188" t="n"/>
+      <c r="N13" s="188" t="n"/>
+      <c r="O13" s="188" t="n"/>
+      <c r="P13" s="188" t="n"/>
+      <c r="Q13" s="188" t="n"/>
+      <c r="R13" s="199" t="n"/>
+      <c r="S13" s="199" t="n"/>
+      <c r="T13" s="199" t="n"/>
+      <c r="U13" s="199" t="n"/>
+    </row>
+    <row r="14" ht="92.40000000000001" customHeight="1">
+      <c r="A14" s="189" t="inlineStr">
+        <is>
+          <t>10. Grease plastic bearning</t>
+        </is>
+      </c>
+      <c r="B14" s="189" t="inlineStr">
+        <is>
+          <t>No grease filled in the bearing</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>S: Portion of production run may have to be scrapped (7)
+OEM: Portion of production run may have to be scrapped (7)
+EU: Degradtion of primary function (7)</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="200" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Severity Test:Defect text matches AIAG standard</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Daily maintenace check sheet
+Preventive Maintenance
+Work instruction for grease refill</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Read switch to find the level of grease in the tank (2)
+Layer Process Audit (6)</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="201" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. “Read switch to find the level of grease in the tank (2)” does not describe error detection/prevention by automated controls that prevent a discrepant part from being made. It is more consistent with a sensor/check used to detect a condition, but the text is not specific enough to support AIAG 2. The Layer Process Audit (6) is also a separate audit-type control and does not support a 2. Recommended Detection: 6</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="R14" s="14" t="n"/>
+      <c r="S14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="201" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="79.2" customHeight="1">
+      <c r="A15" s="203" t="n"/>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Less grease in the bearing</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S: Portion of production run may have to be scrapped (5)
+OEM: Portion of production run may have to be scrapped (7)
+</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="201" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="202" t="inlineStr">
+        <is>
+          <t>'Portion of production run may have to be scrapped' maps to AIAG Severity 7 because a portion of the production run may have to be scrapped. The stated Severity 5 is an under-rating.</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Severity test: Lower severity choosen</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Preventive maintenance
+Calibration of gage</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>First Off Approval (2)
+Layered Process Audit (6)
+Calibration report (6)</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="201" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. The listed controls are audit/calibration/approval activities, not in-station automated error detection or prevention. Specifically, “First Off Approval” aligns more with setup/first-piece verification, “Layered Process Audit” is a random/audited control, and “Calibration report” is administrative documentation rather than a detection control. Recommended Detection: 9</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="R15" s="14" t="n"/>
+      <c r="S15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" s="201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="118.8" customHeight="1">
+      <c r="A16" s="204" t="n"/>
+      <c r="B16" s="205" t="inlineStr">
+        <is>
+          <t>More grease in the bearning</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="200" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Severity Test:Defect text matches AIAG standard</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Daily maintenace check sheet
+Preventive Maintenance
+Work instruction for grease refill</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>First Off Approval (2)
+Layered Process Audit (6)
+Calibration report (6)</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" s="201" t="n">
+        <v>9</v>
+      </c>
+      <c r="N16" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. The listed controls are First Off Approval, Layered Process Audit, and Calibration report, which are not detection controls that detect/prevent the failure mode in the AIAG sense for a 5. “Layered Process Audit” and “Calibration report” are audit/documentation activities, not in-station automated error detection or operator variable gauging with notification. Recommended Detection: 9</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="P16" s="206" t="inlineStr">
+        <is>
+          <t>Gap identified. Det must be &lt;3</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="201" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" s="201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="105.6" customHeight="1">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: No discernible effect (1)</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="200" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="189" t="inlineStr">
+        <is>
+          <t>Severity test scenario: perfect match</t>
+        </is>
+      </c>
+      <c r="I17" s="189" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Severe Semantic Mismatch (Over-rating)</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>"Random visual inspection by supervisor once a shift (3)"</t>
+        </is>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. “Random visual inspection by supervisor once a shift” is a **random audit/post-processing visual check**, which aligns more with **AIAG 9** (difficult to detect) or at best **8** depending on context, not **3**. AIAG 3 requires **in-station automated controls** that detect the discrepant part and automatically lock it in station. Recommended Detection: **9**</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="R17" s="14" t="n"/>
+      <c r="S17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="52.8" customHeight="1">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>EU: Apperance, fit and finish type itms do not confrm, defect noticed by most of the customrs (&gt;75%) (4)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="200" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="n"/>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Severity test scenario: Spelling and typo</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Severe Semantic Mismatch (Under-rating)</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>"In-station automated vision system that locks the machine if a defect is found (8)"</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" s="201" t="n">
+        <v>8</v>
+      </c>
+      <c r="N18" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. “In-station automated vision system that locks the machine if a defect is found” describes **automated in-station detection that locks the part/machine**, which aligns with **AIAG Detection 3**, not 8. Recommended Detection: **3**</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="201" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" s="201" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" ht="105.6" customHeight="1">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="205" t="inlineStr">
+        <is>
+          <t>S: 100% of product may have to be scrapped. Line shutdown or stop ship. (8)
+OEM: A portion of the production run may have to be scrapped. (7)</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="201" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="202" t="inlineStr">
+        <is>
+          <t>'100% of product may have to be scrapped' and 'Line shutdown or stop ship' map to AIAG Severity 8. The stated severity 7 is an under-rating because the highest effect described is 8.</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="n"/>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Severity test scenario: Column Mismatch (Under-reporting)</t>
+        </is>
+      </c>
+      <c r="I19" s="189" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Heavy Typographical Errors</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>"Aoutmated varible gaging with red light buzer to notfy opreator (5)"</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="201" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. The text describes automated variable gauging with a red light/buzzer to notify the operator, which matches AIAG Detection 5; however, the wording is misspelled and does not clearly indicate whether the gauge is performed in-station or on setup/first-piece only. Recommended Detection: 5</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="R19" s="14" t="n"/>
+      <c r="S19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="201" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" s="201" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" ht="52.8" customHeight="1">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Mismatch	EU: Loss of primary function (product inoperable, does not affect safe operation) (4)</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="201" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="202" t="inlineStr">
+        <is>
+          <t>'Loss of primary function' maps to AIAG 8. The stated (4) is an under-rating.</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="n"/>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>Severity test scenario: EU: Loss of primary function (product inoperable, does not affect safe operation) (4)</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Detection test scenario: . Multiple Controls (Stated matches Strongest)</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>"Visual check by operator (8)  Automated laser interlock in-station (3)"</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" s="200" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="R20" s="14" t="n"/>
+      <c r="S20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" s="201" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" ht="39.6" customHeight="1">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>S: Reduced performance</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="201" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="202" t="inlineStr">
+        <is>
+          <t>'Reduced performance' indicates degradation of the primary function, which maps to AIAG Severity 7. The stated Severity 9 is an over-rating because there is no mention of safety, regulation, or warning.</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="189" t="inlineStr">
+        <is>
+          <t>Severity: Irrelevant text</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Multiple Controls (Stated matches Weakest)</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>"Visual check by operator (8) \n Automated laser interlock in-station (3)"</t>
+        </is>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. The text includes both a manual visual check by operator, which aligns more with 8, and an automated in-station laser interlock, which aligns with 3. Since the strongest/lowest AIAG detection number supported by the text is 3, the original stated detection of 8 is not the best match. Recommended Detection: 3</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="R21" s="14" t="n"/>
+      <c r="S21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="W21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" ht="118.8" customHeight="1">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>S: A proportion of the production run may have to be reworked off line and accepted (5)
+OEM: Potential failure mode affects safe operation and/or involves noncompliance with regulations with warning(9)</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" s="200" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="n"/>
+      <c r="H22" s="189" t="inlineStr">
+        <is>
+          <t>DFMEA PFMEA Gap analysis check</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Missing Brackets / Parentheses</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>"Manual attribute go/no-go gauging in station 7"</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" s="200" t="inlineStr">
+        <is>
+          <t>detection controls text matches AIAG detection criteria</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="P22" s="206" t="inlineStr">
+        <is>
+          <t>Gap identified. Det must be &lt;3</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="R22" s="14" t="n"/>
+      <c r="S22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="201" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" s="201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="92.40000000000001" customHeight="1">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>S: Portion of production run may have to be scrapped (7)
+OEM: Portion of production run may have to be scrapped (7)
+EU: Degradtion of primary function (7)</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="200" t="inlineStr">
+        <is>
+          <t>severity is correct</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Severity Test:Defect text matches AIAG standard</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>Detection test scenario: Number Confusions (Scores mixed with specs)</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>"Check 5 times a day using a 2 mm variable gauge (6)"`</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="201" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="202" t="inlineStr">
+        <is>
+          <t>detection controls text keywords do not match AIAG detection criteria. The text describes an in-process variable gauge check, but it does not indicate post-processing detection or use of boundary samples as required for AIAG 6; it sounds more like in-station variable gauging, which aligns better with AIAG 5. Recommended Detection: 5</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>no gap</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="R23" s="14" t="n"/>
+      <c r="S23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="201" t="n">
+        <v>3</v>
+      </c>
+      <c r="W23" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X23" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="47">
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A7:U7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="L5:T5"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="Q8:U8"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="R12:R13"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="W12:W13"/>
+    <mergeCell ref="L6:T6"/>
+    <mergeCell ref="L4:S4"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="Q9:U9"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Q12:Q13"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="B10:K10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="3"/>
+</worksheet>
 </file>